--- a/AAII_Financials/Yearly/MOMO_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/MOMO_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="92">
   <si>
     <t>MOMO</t>
   </si>
@@ -656,196 +656,208 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43100</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42735</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42369</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42004</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41639</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41274</v>
       </c>
-      <c r="O7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>1754200</v>
+        <v>1668600</v>
       </c>
       <c r="E8" s="3">
-        <v>2012600</v>
+        <v>1766100</v>
       </c>
       <c r="F8" s="3">
-        <v>2074500</v>
+        <v>2026300</v>
       </c>
       <c r="G8" s="3">
-        <v>2349400</v>
+        <v>2088700</v>
       </c>
       <c r="H8" s="3">
-        <v>1851400</v>
+        <v>2365400</v>
       </c>
       <c r="I8" s="3">
-        <v>1227000</v>
+        <v>1864000</v>
       </c>
       <c r="J8" s="3">
+        <v>1235400</v>
+      </c>
+      <c r="K8" s="3">
         <v>76400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>19200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>7100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>500</v>
       </c>
-      <c r="N8" s="3">
-        <v>0</v>
-      </c>
-      <c r="O8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="O8" s="3">
+        <v>0</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>1024700</v>
+        <v>976700</v>
       </c>
       <c r="E9" s="3">
-        <v>1157600</v>
+        <v>1031700</v>
       </c>
       <c r="F9" s="3">
-        <v>1101400</v>
+        <v>1165500</v>
       </c>
       <c r="G9" s="3">
-        <v>1172600</v>
+        <v>1108900</v>
       </c>
       <c r="H9" s="3">
-        <v>991800</v>
+        <v>1180600</v>
       </c>
       <c r="I9" s="3">
-        <v>603900</v>
+        <v>998600</v>
       </c>
       <c r="J9" s="3">
+        <v>608000</v>
+      </c>
+      <c r="K9" s="3">
         <v>33300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>4400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>400</v>
       </c>
-      <c r="N9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>729400</v>
+        <v>691900</v>
       </c>
       <c r="E10" s="3">
-        <v>855000</v>
+        <v>734400</v>
       </c>
       <c r="F10" s="3">
-        <v>973100</v>
+        <v>860900</v>
       </c>
       <c r="G10" s="3">
-        <v>1176900</v>
+        <v>979700</v>
       </c>
       <c r="H10" s="3">
-        <v>859600</v>
+        <v>1184900</v>
       </c>
       <c r="I10" s="3">
-        <v>623200</v>
+        <v>865500</v>
       </c>
       <c r="J10" s="3">
+        <v>627400</v>
+      </c>
+      <c r="K10" s="3">
         <v>43000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>14900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>4600</v>
       </c>
-      <c r="M10" s="3">
-        <v>0</v>
-      </c>
-      <c r="N10" s="3" t="s">
-        <v>3</v>
+      <c r="N10" s="3">
+        <v>0</v>
       </c>
       <c r="O10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -862,50 +874,54 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>138900</v>
+        <v>123000</v>
       </c>
       <c r="E12" s="3">
-        <v>156300</v>
+        <v>139900</v>
       </c>
       <c r="F12" s="3">
-        <v>161200</v>
+        <v>157300</v>
       </c>
       <c r="G12" s="3">
-        <v>151200</v>
+        <v>162300</v>
       </c>
       <c r="H12" s="3">
-        <v>105000</v>
+        <v>152200</v>
       </c>
       <c r="I12" s="3">
-        <v>47800</v>
+        <v>105700</v>
       </c>
       <c r="J12" s="3">
+        <v>48100</v>
+      </c>
+      <c r="K12" s="3">
         <v>4300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>3300</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>1500</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>200</v>
       </c>
-      <c r="O12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -945,36 +961,39 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>1600</v>
+      <c r="D14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E14" s="3">
-        <v>609600</v>
+        <v>-16400</v>
       </c>
       <c r="F14" s="3">
-        <v>1400</v>
+        <v>613500</v>
       </c>
       <c r="G14" s="3">
+        <v>-200</v>
+      </c>
+      <c r="H14" s="3">
         <v>2200</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>6000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>4200</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>800</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
@@ -987,9 +1006,12 @@
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1029,9 +1051,12 @@
       <c r="O15" s="3">
         <v>0</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1045,92 +1070,99 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1531000</v>
+        <v>1366200</v>
       </c>
       <c r="E17" s="3">
-        <v>2345100</v>
+        <v>1523400</v>
       </c>
       <c r="F17" s="3">
-        <v>1726400</v>
+        <v>2360700</v>
       </c>
       <c r="G17" s="3">
-        <v>1860800</v>
+        <v>1736500</v>
       </c>
       <c r="H17" s="3">
-        <v>1406400</v>
+        <v>1873400</v>
       </c>
       <c r="I17" s="3">
-        <v>895100</v>
+        <v>1416000</v>
       </c>
       <c r="J17" s="3">
+        <v>901200</v>
+      </c>
+      <c r="K17" s="3">
         <v>57200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>18400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>11200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>600</v>
       </c>
-      <c r="O17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>223200</v>
+        <v>302400</v>
       </c>
       <c r="E18" s="3">
-        <v>-332400</v>
+        <v>242700</v>
       </c>
       <c r="F18" s="3">
-        <v>348100</v>
+        <v>-334400</v>
       </c>
       <c r="G18" s="3">
-        <v>488700</v>
+        <v>352100</v>
       </c>
       <c r="H18" s="3">
-        <v>445000</v>
+        <v>492000</v>
       </c>
       <c r="I18" s="3">
-        <v>332000</v>
+        <v>448100</v>
       </c>
       <c r="J18" s="3">
+        <v>334200</v>
+      </c>
+      <c r="K18" s="3">
         <v>19200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-4100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-1400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-600</v>
       </c>
-      <c r="O18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1147,115 +1179,122 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>68800</v>
+        <v>75000</v>
       </c>
       <c r="E20" s="3">
-        <v>53300</v>
+        <v>51300</v>
       </c>
       <c r="F20" s="3">
-        <v>63000</v>
+        <v>53400</v>
       </c>
       <c r="G20" s="3">
-        <v>56300</v>
+        <v>61800</v>
       </c>
       <c r="H20" s="3">
-        <v>37700</v>
+        <v>56700</v>
       </c>
       <c r="I20" s="3">
-        <v>20100</v>
+        <v>37900</v>
       </c>
       <c r="J20" s="3">
-        <v>1100</v>
+        <v>20200</v>
       </c>
       <c r="K20" s="3">
         <v>1100</v>
       </c>
       <c r="L20" s="3">
+        <v>1100</v>
+      </c>
+      <c r="M20" s="3">
         <v>100</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
         <v>0</v>
       </c>
-      <c r="O20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>307500</v>
+        <v>393000</v>
       </c>
       <c r="E21" s="3">
-        <v>-242600</v>
+        <v>330800</v>
       </c>
       <c r="F21" s="3">
-        <v>461700</v>
+        <v>-230000</v>
       </c>
       <c r="G21" s="3">
-        <v>594100</v>
+        <v>463500</v>
       </c>
       <c r="H21" s="3">
-        <v>516000</v>
+        <v>582200</v>
       </c>
       <c r="I21" s="3">
-        <v>363600</v>
+        <v>497700</v>
       </c>
       <c r="J21" s="3">
+        <v>355600</v>
+      </c>
+      <c r="K21" s="3">
         <v>21400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>2900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-3600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-1300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-500</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>11500</v>
+        <v>8700</v>
       </c>
       <c r="E22" s="3">
-        <v>10200</v>
+        <v>11600</v>
       </c>
       <c r="F22" s="3">
+        <v>10300</v>
+      </c>
+      <c r="G22" s="3">
+        <v>11000</v>
+      </c>
+      <c r="H22" s="3">
         <v>10900</v>
       </c>
-      <c r="G22" s="3">
-        <v>10900</v>
-      </c>
-      <c r="H22" s="3">
-        <v>7800</v>
-      </c>
       <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>3</v>
+        <v>7900</v>
+      </c>
+      <c r="J22" s="3">
+        <v>0</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>3</v>
@@ -1269,81 +1308,87 @@
       <c r="N22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
-      </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="O22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>280500</v>
+        <v>368700</v>
       </c>
       <c r="E23" s="3">
-        <v>-289300</v>
+        <v>282400</v>
       </c>
       <c r="F23" s="3">
-        <v>400200</v>
+        <v>-291300</v>
       </c>
       <c r="G23" s="3">
-        <v>534100</v>
+        <v>403000</v>
       </c>
       <c r="H23" s="3">
-        <v>474900</v>
+        <v>537700</v>
       </c>
       <c r="I23" s="3">
-        <v>352100</v>
+        <v>478200</v>
       </c>
       <c r="J23" s="3">
+        <v>354500</v>
+      </c>
+      <c r="K23" s="3">
         <v>20300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-4000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-1400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-600</v>
       </c>
-      <c r="O23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>77600</v>
+        <v>87600</v>
       </c>
       <c r="E24" s="3">
-        <v>113600</v>
+        <v>78200</v>
       </c>
       <c r="F24" s="3">
-        <v>104300</v>
+        <v>114400</v>
       </c>
       <c r="G24" s="3">
-        <v>122000</v>
+        <v>105000</v>
       </c>
       <c r="H24" s="3">
-        <v>96600</v>
+        <v>122900</v>
       </c>
       <c r="I24" s="3">
-        <v>61400</v>
+        <v>97300</v>
       </c>
       <c r="J24" s="3">
+        <v>61900</v>
+      </c>
+      <c r="K24" s="3">
         <v>700</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
       <c r="L24" s="3">
         <v>0</v>
       </c>
@@ -1353,12 +1398,15 @@
       <c r="N24" s="3">
         <v>0</v>
       </c>
-      <c r="O24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="O24" s="3">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1398,93 +1446,102 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>202800</v>
+        <v>281100</v>
       </c>
       <c r="E26" s="3">
-        <v>-402900</v>
+        <v>204200</v>
       </c>
       <c r="F26" s="3">
-        <v>295900</v>
+        <v>-405600</v>
       </c>
       <c r="G26" s="3">
-        <v>412000</v>
+        <v>297900</v>
       </c>
       <c r="H26" s="3">
-        <v>378300</v>
+        <v>414900</v>
       </c>
       <c r="I26" s="3">
-        <v>290600</v>
+        <v>380900</v>
       </c>
       <c r="J26" s="3">
+        <v>292600</v>
+      </c>
+      <c r="K26" s="3">
         <v>19600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-4000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-1400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-600</v>
       </c>
-      <c r="O26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>204900</v>
+        <v>272100</v>
       </c>
       <c r="E27" s="3">
-        <v>-402300</v>
+        <v>206300</v>
       </c>
       <c r="F27" s="3">
-        <v>290400</v>
+        <v>-405100</v>
       </c>
       <c r="G27" s="3">
-        <v>410200</v>
+        <v>292400</v>
       </c>
       <c r="H27" s="3">
-        <v>388800</v>
+        <v>413000</v>
       </c>
       <c r="I27" s="3">
-        <v>296600</v>
+        <v>391400</v>
       </c>
       <c r="J27" s="3">
+        <v>298600</v>
+      </c>
+      <c r="K27" s="3">
         <v>19600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-13100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-2700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-1000</v>
       </c>
-      <c r="O27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1524,9 +1581,12 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1566,9 +1626,12 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1608,9 +1671,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1650,93 +1716,102 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-68800</v>
+        <v>-75000</v>
       </c>
       <c r="E32" s="3">
-        <v>-53300</v>
+        <v>-51300</v>
       </c>
       <c r="F32" s="3">
-        <v>-63000</v>
+        <v>-53400</v>
       </c>
       <c r="G32" s="3">
-        <v>-56300</v>
+        <v>-61800</v>
       </c>
       <c r="H32" s="3">
-        <v>-37700</v>
+        <v>-56700</v>
       </c>
       <c r="I32" s="3">
-        <v>-20100</v>
+        <v>-37900</v>
       </c>
       <c r="J32" s="3">
-        <v>-1100</v>
+        <v>-20200</v>
       </c>
       <c r="K32" s="3">
         <v>-1100</v>
       </c>
       <c r="L32" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="M32" s="3">
         <v>-100</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
         <v>0</v>
       </c>
-      <c r="O32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>204900</v>
+        <v>272100</v>
       </c>
       <c r="E33" s="3">
-        <v>-402300</v>
+        <v>206300</v>
       </c>
       <c r="F33" s="3">
-        <v>290400</v>
+        <v>-405100</v>
       </c>
       <c r="G33" s="3">
-        <v>410200</v>
+        <v>292400</v>
       </c>
       <c r="H33" s="3">
-        <v>388800</v>
+        <v>413000</v>
       </c>
       <c r="I33" s="3">
-        <v>296600</v>
+        <v>391400</v>
       </c>
       <c r="J33" s="3">
+        <v>298600</v>
+      </c>
+      <c r="K33" s="3">
         <v>19600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-13100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-2700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-1000</v>
       </c>
-      <c r="O33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1776,98 +1851,107 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>204900</v>
+        <v>272100</v>
       </c>
       <c r="E35" s="3">
-        <v>-402300</v>
+        <v>206300</v>
       </c>
       <c r="F35" s="3">
-        <v>290400</v>
+        <v>-405100</v>
       </c>
       <c r="G35" s="3">
-        <v>410200</v>
+        <v>292400</v>
       </c>
       <c r="H35" s="3">
-        <v>388800</v>
+        <v>413000</v>
       </c>
       <c r="I35" s="3">
-        <v>296600</v>
+        <v>391400</v>
       </c>
       <c r="J35" s="3">
+        <v>298600</v>
+      </c>
+      <c r="K35" s="3">
         <v>19600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-13100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-2700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-1000</v>
       </c>
-      <c r="O35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43100</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42735</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42369</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42004</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41639</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41274</v>
       </c>
-      <c r="O38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1884,8 +1968,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1902,80 +1987,84 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>692900</v>
+        <v>781400</v>
       </c>
       <c r="E41" s="3">
-        <v>769200</v>
+        <v>697600</v>
       </c>
       <c r="F41" s="3">
-        <v>464500</v>
+        <v>774400</v>
       </c>
       <c r="G41" s="3">
-        <v>360800</v>
+        <v>467700</v>
       </c>
       <c r="H41" s="3">
-        <v>340800</v>
+        <v>363200</v>
       </c>
       <c r="I41" s="3">
-        <v>616100</v>
+        <v>343100</v>
       </c>
       <c r="J41" s="3">
+        <v>620300</v>
+      </c>
+      <c r="K41" s="3">
         <v>35600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>24300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>71100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>8400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2700</v>
       </c>
-      <c r="O41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>773300</v>
+        <v>176600</v>
       </c>
       <c r="E42" s="3">
-        <v>394900</v>
+        <v>778500</v>
       </c>
       <c r="F42" s="3">
-        <v>1044700</v>
+        <v>397600</v>
       </c>
       <c r="G42" s="3">
-        <v>1700100</v>
+        <v>1051900</v>
       </c>
       <c r="H42" s="3">
-        <v>1218500</v>
+        <v>1711700</v>
       </c>
       <c r="I42" s="3">
-        <v>337300</v>
+        <v>1226800</v>
       </c>
       <c r="J42" s="3">
+        <v>339600</v>
+      </c>
+      <c r="K42" s="3">
         <v>54400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>43100</v>
       </c>
-      <c r="L42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M42" s="3" t="s">
         <v>3</v>
       </c>
@@ -1985,51 +2074,57 @@
       <c r="O42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>115500</v>
+        <v>29000</v>
       </c>
       <c r="E43" s="3">
-        <v>110700</v>
+        <v>116300</v>
       </c>
       <c r="F43" s="3">
-        <v>82900</v>
+        <v>111500</v>
       </c>
       <c r="G43" s="3">
-        <v>72200</v>
+        <v>83400</v>
       </c>
       <c r="H43" s="3">
-        <v>120900</v>
+        <v>72700</v>
       </c>
       <c r="I43" s="3">
-        <v>56600</v>
+        <v>121700</v>
       </c>
       <c r="J43" s="3">
+        <v>57000</v>
+      </c>
+      <c r="K43" s="3">
         <v>6100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>100</v>
       </c>
-      <c r="O43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2069,201 +2164,216 @@
       <c r="O44" s="3">
         <v>0</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P44" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>37200</v>
+        <v>102000</v>
       </c>
       <c r="E45" s="3">
-        <v>24600</v>
+        <v>37500</v>
       </c>
       <c r="F45" s="3">
-        <v>29900</v>
+        <v>24800</v>
       </c>
       <c r="G45" s="3">
-        <v>47700</v>
+        <v>30100</v>
       </c>
       <c r="H45" s="3">
-        <v>64200</v>
+        <v>48100</v>
       </c>
       <c r="I45" s="3">
-        <v>63400</v>
+        <v>64600</v>
       </c>
       <c r="J45" s="3">
+        <v>63800</v>
+      </c>
+      <c r="K45" s="3">
         <v>3400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>100</v>
       </c>
-      <c r="N45" s="3">
-        <v>0</v>
-      </c>
-      <c r="O45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="O45" s="3">
+        <v>0</v>
+      </c>
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>1618900</v>
+        <v>1089000</v>
       </c>
       <c r="E46" s="3">
-        <v>1299500</v>
+        <v>1629900</v>
       </c>
       <c r="F46" s="3">
-        <v>1622000</v>
+        <v>1308300</v>
       </c>
       <c r="G46" s="3">
-        <v>2180800</v>
+        <v>1633000</v>
       </c>
       <c r="H46" s="3">
-        <v>1744400</v>
+        <v>2195700</v>
       </c>
       <c r="I46" s="3">
-        <v>1067900</v>
+        <v>1756300</v>
       </c>
       <c r="J46" s="3">
+        <v>1075200</v>
+      </c>
+      <c r="K46" s="3">
         <v>99400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>72400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>73500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>8900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2800</v>
       </c>
-      <c r="O46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>123400</v>
+        <v>112200</v>
       </c>
       <c r="E47" s="3">
-        <v>113200</v>
+        <v>124300</v>
       </c>
       <c r="F47" s="3">
-        <v>62800</v>
+        <v>114000</v>
       </c>
       <c r="G47" s="3">
-        <v>68500</v>
+        <v>63300</v>
       </c>
       <c r="H47" s="3">
-        <v>61800</v>
+        <v>68900</v>
       </c>
       <c r="I47" s="3">
-        <v>39800</v>
+        <v>62200</v>
       </c>
       <c r="J47" s="3">
+        <v>40100</v>
+      </c>
+      <c r="K47" s="3">
         <v>4400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>2800</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>100</v>
       </c>
-      <c r="N47" s="3">
-        <v>0</v>
-      </c>
-      <c r="O47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="O47" s="3">
+        <v>0</v>
+      </c>
+      <c r="P47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>39800</v>
+        <v>106900</v>
       </c>
       <c r="E48" s="3">
-        <v>60600</v>
+        <v>40100</v>
       </c>
       <c r="F48" s="3">
-        <v>75100</v>
+        <v>61000</v>
       </c>
       <c r="G48" s="3">
-        <v>74100</v>
+        <v>75600</v>
       </c>
       <c r="H48" s="3">
-        <v>53500</v>
+        <v>74600</v>
       </c>
       <c r="I48" s="3">
-        <v>35700</v>
+        <v>53900</v>
       </c>
       <c r="J48" s="3">
+        <v>36000</v>
+      </c>
+      <c r="K48" s="3">
         <v>1900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>100</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E49" s="3">
         <v>3100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>3800</v>
       </c>
-      <c r="F49" s="3">
-        <v>659400</v>
-      </c>
       <c r="G49" s="3">
-        <v>725000</v>
+        <v>663900</v>
       </c>
       <c r="H49" s="3">
-        <v>737900</v>
+        <v>730000</v>
       </c>
       <c r="I49" s="3">
+        <v>742900</v>
+      </c>
+      <c r="J49" s="3">
         <v>9800</v>
       </c>
-      <c r="J49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2279,9 +2389,12 @@
       <c r="O49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2321,9 +2434,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2363,51 +2479,57 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>400500</v>
+        <v>945600</v>
       </c>
       <c r="E52" s="3">
-        <v>1023800</v>
+        <v>403200</v>
       </c>
       <c r="F52" s="3">
-        <v>786900</v>
+        <v>1030800</v>
       </c>
       <c r="G52" s="3">
-        <v>56100</v>
+        <v>792300</v>
       </c>
       <c r="H52" s="3">
-        <v>21200</v>
+        <v>56500</v>
       </c>
       <c r="I52" s="3">
-        <v>16500</v>
+        <v>21300</v>
       </c>
       <c r="J52" s="3">
+        <v>16600</v>
+      </c>
+      <c r="K52" s="3">
         <v>500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>100</v>
       </c>
-      <c r="M52" s="3">
-        <v>0</v>
-      </c>
-      <c r="N52" s="3" t="s">
-        <v>3</v>
+      <c r="N52" s="3">
+        <v>0</v>
       </c>
       <c r="O52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2447,51 +2569,57 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>2185700</v>
+        <v>2256000</v>
       </c>
       <c r="E54" s="3">
-        <v>2500800</v>
+        <v>2200600</v>
       </c>
       <c r="F54" s="3">
-        <v>3206300</v>
+        <v>2517800</v>
       </c>
       <c r="G54" s="3">
-        <v>3104500</v>
+        <v>3228100</v>
       </c>
       <c r="H54" s="3">
-        <v>2618800</v>
+        <v>3125700</v>
       </c>
       <c r="I54" s="3">
-        <v>1169700</v>
+        <v>2636600</v>
       </c>
       <c r="J54" s="3">
+        <v>1177700</v>
+      </c>
+      <c r="K54" s="3">
         <v>106300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>77900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>75500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>9600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>3000</v>
       </c>
-      <c r="O54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2508,8 +2636,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2526,58 +2655,62 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>85200</v>
+        <v>85700</v>
       </c>
       <c r="E57" s="3">
-        <v>100300</v>
+        <v>85800</v>
       </c>
       <c r="F57" s="3">
-        <v>96600</v>
+        <v>101000</v>
       </c>
       <c r="G57" s="3">
-        <v>98600</v>
+        <v>97200</v>
       </c>
       <c r="H57" s="3">
-        <v>99200</v>
+        <v>99300</v>
       </c>
       <c r="I57" s="3">
-        <v>67000</v>
+        <v>99900</v>
       </c>
       <c r="J57" s="3">
+        <v>67400</v>
+      </c>
+      <c r="K57" s="3">
         <v>5600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>100</v>
       </c>
-      <c r="N57" s="3">
-        <v>0</v>
-      </c>
-      <c r="O57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="O57" s="3">
+        <v>0</v>
+      </c>
+      <c r="P57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>365400</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>3</v>
+        <v>30000</v>
+      </c>
+      <c r="E58" s="3">
+        <v>367900</v>
       </c>
       <c r="F58" s="3" t="s">
         <v>3</v>
@@ -2594,8 +2727,8 @@
       <c r="J58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
+      <c r="K58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L58" s="3">
         <v>0</v>
@@ -2609,113 +2742,122 @@
       <c r="O58" s="3">
         <v>0</v>
       </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>203700</v>
+        <v>175100</v>
       </c>
       <c r="E59" s="3">
-        <v>247100</v>
+        <v>205100</v>
       </c>
       <c r="F59" s="3">
-        <v>250900</v>
+        <v>248800</v>
       </c>
       <c r="G59" s="3">
-        <v>261300</v>
+        <v>252600</v>
       </c>
       <c r="H59" s="3">
-        <v>273100</v>
+        <v>263100</v>
       </c>
       <c r="I59" s="3">
-        <v>166700</v>
+        <v>275000</v>
       </c>
       <c r="J59" s="3">
+        <v>167800</v>
+      </c>
+      <c r="K59" s="3">
         <v>12900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>8800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>5100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>800</v>
       </c>
-      <c r="N59" s="3">
-        <v>0</v>
-      </c>
-      <c r="O59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="O59" s="3">
+        <v>0</v>
+      </c>
+      <c r="P59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>654300</v>
+        <v>290800</v>
       </c>
       <c r="E60" s="3">
-        <v>347400</v>
+        <v>658700</v>
       </c>
       <c r="F60" s="3">
-        <v>347500</v>
+        <v>349700</v>
       </c>
       <c r="G60" s="3">
-        <v>359900</v>
+        <v>349900</v>
       </c>
       <c r="H60" s="3">
-        <v>372300</v>
+        <v>362400</v>
       </c>
       <c r="I60" s="3">
-        <v>233600</v>
+        <v>374800</v>
       </c>
       <c r="J60" s="3">
+        <v>235200</v>
+      </c>
+      <c r="K60" s="3">
         <v>18500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>10300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>6000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>800</v>
       </c>
-      <c r="N60" s="3">
-        <v>0</v>
-      </c>
-      <c r="O60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="O60" s="3">
+        <v>0</v>
+      </c>
+      <c r="P60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>272200</v>
       </c>
       <c r="E61" s="3">
-        <v>630400</v>
+        <v>0</v>
       </c>
       <c r="F61" s="3">
-        <v>643300</v>
+        <v>634700</v>
       </c>
       <c r="G61" s="3">
-        <v>684100</v>
+        <v>647700</v>
       </c>
       <c r="H61" s="3">
-        <v>673400</v>
+        <v>688800</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>678000</v>
       </c>
       <c r="J61" s="3">
         <v>0</v>
@@ -2735,38 +2877,41 @@
       <c r="O61" s="3">
         <v>0</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>22200</v>
+        <v>26600</v>
       </c>
       <c r="E62" s="3">
-        <v>61400</v>
+        <v>22300</v>
       </c>
       <c r="F62" s="3">
-        <v>167000</v>
+        <v>61800</v>
       </c>
       <c r="G62" s="3">
-        <v>166200</v>
+        <v>168100</v>
       </c>
       <c r="H62" s="3">
-        <v>51000</v>
+        <v>167400</v>
       </c>
       <c r="I62" s="3">
-        <v>3700</v>
+        <v>51300</v>
       </c>
       <c r="J62" s="3">
-        <v>300</v>
+        <v>3800</v>
       </c>
       <c r="K62" s="3">
         <v>300</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>3</v>
+      <c r="L62" s="3">
+        <v>300</v>
       </c>
       <c r="M62" s="3" t="s">
         <v>3</v>
@@ -2777,9 +2922,12 @@
       <c r="O62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2819,9 +2967,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2861,9 +3012,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2903,51 +3057,57 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>697600</v>
+        <v>589600</v>
       </c>
       <c r="E66" s="3">
-        <v>1058300</v>
+        <v>702400</v>
       </c>
       <c r="F66" s="3">
-        <v>1184900</v>
+        <v>1065500</v>
       </c>
       <c r="G66" s="3">
-        <v>1236300</v>
+        <v>1193000</v>
       </c>
       <c r="H66" s="3">
-        <v>1109500</v>
+        <v>1244700</v>
       </c>
       <c r="I66" s="3">
-        <v>239900</v>
+        <v>1117000</v>
       </c>
       <c r="J66" s="3">
+        <v>241600</v>
+      </c>
+      <c r="K66" s="3">
         <v>18700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>10600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>6000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>800</v>
       </c>
-      <c r="N66" s="3">
-        <v>0</v>
-      </c>
-      <c r="O66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="O66" s="3">
+        <v>0</v>
+      </c>
+      <c r="P66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2964,8 +3124,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3005,9 +3166,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3047,9 +3211,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3081,17 +3248,20 @@
         <v>0</v>
       </c>
       <c r="M70" s="3">
+        <v>0</v>
+      </c>
+      <c r="N70" s="3">
         <v>12200</v>
       </c>
-      <c r="N70" s="3">
+      <c r="O70" s="3">
         <v>3900</v>
       </c>
-      <c r="O70" s="3">
-        <v>0</v>
-      </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3131,51 +3301,57 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3">
-        <v>734700</v>
+      <c r="D72" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E72" s="3">
-        <v>645900</v>
+        <v>739700</v>
       </c>
       <c r="F72" s="3">
-        <v>1166000</v>
+        <v>650300</v>
       </c>
       <c r="G72" s="3">
-        <v>1030700</v>
+        <v>1173900</v>
       </c>
       <c r="H72" s="3">
-        <v>740300</v>
+        <v>1037700</v>
       </c>
       <c r="I72" s="3">
-        <v>351500</v>
+        <v>745300</v>
       </c>
       <c r="J72" s="3">
+        <v>353900</v>
+      </c>
+      <c r="K72" s="3">
         <v>7100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-13500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-17000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-3800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-1000</v>
       </c>
-      <c r="O72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3215,9 +3391,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3257,9 +3436,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3299,51 +3481,57 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>1488100</v>
+        <v>1666400</v>
       </c>
       <c r="E76" s="3">
-        <v>1442500</v>
+        <v>1498300</v>
       </c>
       <c r="F76" s="3">
-        <v>2021400</v>
+        <v>1452300</v>
       </c>
       <c r="G76" s="3">
-        <v>1868200</v>
+        <v>2035100</v>
       </c>
       <c r="H76" s="3">
-        <v>1509300</v>
+        <v>1880900</v>
       </c>
       <c r="I76" s="3">
-        <v>929800</v>
+        <v>1519600</v>
       </c>
       <c r="J76" s="3">
+        <v>936100</v>
+      </c>
+      <c r="K76" s="3">
         <v>87500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>67300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>69500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-3500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-900</v>
       </c>
-      <c r="O76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3383,98 +3571,107 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43100</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42735</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42369</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42004</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41639</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41274</v>
       </c>
-      <c r="O80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>204900</v>
+        <v>272100</v>
       </c>
       <c r="E81" s="3">
-        <v>-402300</v>
+        <v>206300</v>
       </c>
       <c r="F81" s="3">
-        <v>290400</v>
+        <v>-405100</v>
       </c>
       <c r="G81" s="3">
-        <v>410200</v>
+        <v>292400</v>
       </c>
       <c r="H81" s="3">
-        <v>388800</v>
+        <v>413000</v>
       </c>
       <c r="I81" s="3">
-        <v>296600</v>
+        <v>391400</v>
       </c>
       <c r="J81" s="3">
+        <v>298600</v>
+      </c>
+      <c r="K81" s="3">
         <v>19600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-13100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-2700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-1000</v>
       </c>
-      <c r="O81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3491,50 +3688,54 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>15500</v>
+        <v>11100</v>
       </c>
       <c r="E83" s="3">
-        <v>36500</v>
+        <v>15600</v>
       </c>
       <c r="F83" s="3">
-        <v>50600</v>
+        <v>36800</v>
       </c>
       <c r="G83" s="3">
-        <v>49200</v>
+        <v>50900</v>
       </c>
       <c r="H83" s="3">
-        <v>33300</v>
+        <v>49500</v>
       </c>
       <c r="I83" s="3">
+        <v>33500</v>
+      </c>
+      <c r="J83" s="3">
         <v>11600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>100</v>
       </c>
-      <c r="N83" s="3">
-        <v>0</v>
-      </c>
-      <c r="O83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="O83" s="3">
+        <v>0</v>
+      </c>
+      <c r="P83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3574,9 +3775,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3616,9 +3820,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3658,9 +3865,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3700,9 +3910,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3742,51 +3955,57 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>169400</v>
+        <v>316600</v>
       </c>
       <c r="E89" s="3">
-        <v>215300</v>
+        <v>170600</v>
       </c>
       <c r="F89" s="3">
-        <v>425400</v>
+        <v>216800</v>
       </c>
       <c r="G89" s="3">
-        <v>752400</v>
+        <v>428300</v>
       </c>
       <c r="H89" s="3">
-        <v>459500</v>
+        <v>757500</v>
       </c>
       <c r="I89" s="3">
-        <v>398500</v>
+        <v>462600</v>
       </c>
       <c r="J89" s="3">
+        <v>401200</v>
+      </c>
+      <c r="K89" s="3">
         <v>30100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>8200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-600</v>
       </c>
-      <c r="O89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3803,50 +4022,54 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-11100</v>
+        <v>-80100</v>
       </c>
       <c r="E91" s="3">
-        <v>-13200</v>
+        <v>-11200</v>
       </c>
       <c r="F91" s="3">
-        <v>-17100</v>
+        <v>-13300</v>
       </c>
       <c r="G91" s="3">
-        <v>-25800</v>
+        <v>-17300</v>
       </c>
       <c r="H91" s="3">
-        <v>-33500</v>
+        <v>-25900</v>
       </c>
       <c r="I91" s="3">
-        <v>-30200</v>
+        <v>-33800</v>
       </c>
       <c r="J91" s="3">
+        <v>-30400</v>
+      </c>
+      <c r="K91" s="3">
         <v>-1000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-100</v>
       </c>
-      <c r="O91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3886,9 +4109,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3928,51 +4154,57 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>236900</v>
+        <v>335500</v>
       </c>
       <c r="E94" s="3">
-        <v>352200</v>
+        <v>238500</v>
       </c>
       <c r="F94" s="3">
-        <v>-103300</v>
+        <v>354500</v>
       </c>
       <c r="G94" s="3">
-        <v>-556500</v>
+        <v>-104100</v>
       </c>
       <c r="H94" s="3">
-        <v>-1385500</v>
+        <v>-560200</v>
       </c>
       <c r="I94" s="3">
-        <v>-26000</v>
+        <v>-1394900</v>
       </c>
       <c r="J94" s="3">
+        <v>-26200</v>
+      </c>
+      <c r="K94" s="3">
         <v>-16300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-47900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-300</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3989,25 +4221,26 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-116100</v>
+        <v>-133200</v>
       </c>
       <c r="E96" s="3">
-        <v>-117700</v>
+        <v>-116900</v>
       </c>
       <c r="F96" s="3">
-        <v>-155200</v>
+        <v>-118500</v>
       </c>
       <c r="G96" s="3">
-        <v>-121100</v>
+        <v>-156300</v>
       </c>
       <c r="H96" s="3">
-        <v>0</v>
+        <v>-122000</v>
       </c>
       <c r="I96" s="3">
         <v>0</v>
@@ -4030,9 +4263,12 @@
       <c r="O96" s="3">
         <v>0</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4072,9 +4308,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4114,9 +4353,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4156,133 +4398,145 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-474000</v>
+        <v>-236300</v>
       </c>
       <c r="E100" s="3">
-        <v>-246700</v>
+        <v>-477200</v>
       </c>
       <c r="F100" s="3">
-        <v>-206900</v>
+        <v>-248400</v>
       </c>
       <c r="G100" s="3">
-        <v>-175900</v>
+        <v>-208300</v>
       </c>
       <c r="H100" s="3">
-        <v>647300</v>
+        <v>-177100</v>
       </c>
       <c r="I100" s="3">
+        <v>651700</v>
+      </c>
+      <c r="J100" s="3">
         <v>400</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
       <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
         <v>-300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>65000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>6800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>3400</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>5700</v>
+        <v>13100</v>
       </c>
       <c r="E101" s="3">
+        <v>5800</v>
+      </c>
+      <c r="F101" s="3">
         <v>-5800</v>
       </c>
-      <c r="F101" s="3">
-        <v>-11200</v>
-      </c>
       <c r="G101" s="3">
+        <v>-11300</v>
+      </c>
+      <c r="H101" s="3">
         <v>-100</v>
       </c>
-      <c r="H101" s="3">
-        <v>3300</v>
-      </c>
       <c r="I101" s="3">
+        <v>3400</v>
+      </c>
+      <c r="J101" s="3">
         <v>-3700</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-1600</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-200</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
-      </c>
       <c r="N101" s="3">
         <v>0</v>
       </c>
-      <c r="O101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="O101" s="3">
+        <v>0</v>
+      </c>
+      <c r="P101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-61900</v>
+        <v>428800</v>
       </c>
       <c r="E102" s="3">
-        <v>315000</v>
+        <v>-62300</v>
       </c>
       <c r="F102" s="3">
-        <v>104000</v>
+        <v>317100</v>
       </c>
       <c r="G102" s="3">
-        <v>20000</v>
+        <v>104700</v>
       </c>
       <c r="H102" s="3">
-        <v>-275400</v>
+        <v>20100</v>
       </c>
       <c r="I102" s="3">
-        <v>369200</v>
+        <v>-277200</v>
       </c>
       <c r="J102" s="3">
+        <v>371700</v>
+      </c>
+      <c r="K102" s="3">
         <v>12200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-40400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>62400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>5600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>2500</v>
       </c>
-      <c r="O102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P102" s="3"/>
+      <c r="P102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/MOMO_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/MOMO_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="92">
   <si>
     <t>MOMO</t>
   </si>
@@ -727,25 +727,25 @@
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>1668600</v>
+        <v>1658200</v>
       </c>
       <c r="E8" s="3">
-        <v>1766100</v>
+        <v>1755200</v>
       </c>
       <c r="F8" s="3">
-        <v>2026300</v>
+        <v>2013800</v>
       </c>
       <c r="G8" s="3">
-        <v>2088700</v>
+        <v>2075700</v>
       </c>
       <c r="H8" s="3">
-        <v>2365400</v>
+        <v>2350800</v>
       </c>
       <c r="I8" s="3">
-        <v>1864000</v>
+        <v>1852500</v>
       </c>
       <c r="J8" s="3">
-        <v>1235400</v>
+        <v>1227700</v>
       </c>
       <c r="K8" s="3">
         <v>76400</v>
@@ -772,25 +772,25 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>976700</v>
+        <v>970600</v>
       </c>
       <c r="E9" s="3">
-        <v>1031700</v>
+        <v>1025300</v>
       </c>
       <c r="F9" s="3">
-        <v>1165500</v>
+        <v>1158300</v>
       </c>
       <c r="G9" s="3">
-        <v>1108900</v>
+        <v>1102100</v>
       </c>
       <c r="H9" s="3">
-        <v>1180600</v>
+        <v>1173300</v>
       </c>
       <c r="I9" s="3">
-        <v>998600</v>
+        <v>992400</v>
       </c>
       <c r="J9" s="3">
-        <v>608000</v>
+        <v>604200</v>
       </c>
       <c r="K9" s="3">
         <v>33300</v>
@@ -817,25 +817,25 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>691900</v>
+        <v>687600</v>
       </c>
       <c r="E10" s="3">
-        <v>734400</v>
+        <v>729900</v>
       </c>
       <c r="F10" s="3">
-        <v>860900</v>
+        <v>855500</v>
       </c>
       <c r="G10" s="3">
-        <v>979700</v>
+        <v>973700</v>
       </c>
       <c r="H10" s="3">
-        <v>1184900</v>
+        <v>1177500</v>
       </c>
       <c r="I10" s="3">
-        <v>865500</v>
+        <v>860100</v>
       </c>
       <c r="J10" s="3">
-        <v>627400</v>
+        <v>623500</v>
       </c>
       <c r="K10" s="3">
         <v>43000</v>
@@ -881,25 +881,25 @@
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>123000</v>
+        <v>122200</v>
       </c>
       <c r="E12" s="3">
-        <v>139900</v>
+        <v>139000</v>
       </c>
       <c r="F12" s="3">
-        <v>157300</v>
+        <v>156400</v>
       </c>
       <c r="G12" s="3">
-        <v>162300</v>
+        <v>161300</v>
       </c>
       <c r="H12" s="3">
-        <v>152200</v>
+        <v>151300</v>
       </c>
       <c r="I12" s="3">
-        <v>105700</v>
+        <v>105100</v>
       </c>
       <c r="J12" s="3">
-        <v>48100</v>
+        <v>47800</v>
       </c>
       <c r="K12" s="3">
         <v>4300</v>
@@ -970,14 +970,14 @@
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
+      <c r="D14" s="3">
+        <v>3700</v>
       </c>
       <c r="E14" s="3">
-        <v>-16400</v>
+        <v>-16300</v>
       </c>
       <c r="F14" s="3">
-        <v>613500</v>
+        <v>609700</v>
       </c>
       <c r="G14" s="3">
         <v>-200</v>
@@ -1077,25 +1077,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1366200</v>
+        <v>1343500</v>
       </c>
       <c r="E17" s="3">
-        <v>1523400</v>
+        <v>1514000</v>
       </c>
       <c r="F17" s="3">
-        <v>2360700</v>
+        <v>2346100</v>
       </c>
       <c r="G17" s="3">
-        <v>1736500</v>
+        <v>1725800</v>
       </c>
       <c r="H17" s="3">
-        <v>1873400</v>
+        <v>1861900</v>
       </c>
       <c r="I17" s="3">
-        <v>1416000</v>
+        <v>1407200</v>
       </c>
       <c r="J17" s="3">
-        <v>901200</v>
+        <v>895600</v>
       </c>
       <c r="K17" s="3">
         <v>57200</v>
@@ -1122,25 +1122,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>302400</v>
+        <v>314800</v>
       </c>
       <c r="E18" s="3">
-        <v>242700</v>
+        <v>241200</v>
       </c>
       <c r="F18" s="3">
-        <v>-334400</v>
+        <v>-332400</v>
       </c>
       <c r="G18" s="3">
-        <v>352100</v>
+        <v>350000</v>
       </c>
       <c r="H18" s="3">
-        <v>492000</v>
+        <v>488900</v>
       </c>
       <c r="I18" s="3">
-        <v>448100</v>
+        <v>445300</v>
       </c>
       <c r="J18" s="3">
-        <v>334200</v>
+        <v>332200</v>
       </c>
       <c r="K18" s="3">
         <v>19200</v>
@@ -1186,25 +1186,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>75000</v>
+        <v>60300</v>
       </c>
       <c r="E20" s="3">
-        <v>51300</v>
+        <v>51000</v>
       </c>
       <c r="F20" s="3">
-        <v>53400</v>
+        <v>53100</v>
       </c>
       <c r="G20" s="3">
-        <v>61800</v>
+        <v>61400</v>
       </c>
       <c r="H20" s="3">
-        <v>56700</v>
+        <v>56300</v>
       </c>
       <c r="I20" s="3">
-        <v>37900</v>
+        <v>37700</v>
       </c>
       <c r="J20" s="3">
-        <v>20200</v>
+        <v>20100</v>
       </c>
       <c r="K20" s="3">
         <v>1100</v>
@@ -1231,25 +1231,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>393000</v>
+        <v>386000</v>
       </c>
       <c r="E21" s="3">
-        <v>330800</v>
+        <v>307600</v>
       </c>
       <c r="F21" s="3">
-        <v>-230000</v>
+        <v>-242800</v>
       </c>
       <c r="G21" s="3">
-        <v>463500</v>
+        <v>461800</v>
       </c>
       <c r="H21" s="3">
-        <v>582200</v>
+        <v>594400</v>
       </c>
       <c r="I21" s="3">
-        <v>497700</v>
+        <v>516300</v>
       </c>
       <c r="J21" s="3">
-        <v>355600</v>
+        <v>363800</v>
       </c>
       <c r="K21" s="3">
         <v>21400</v>
@@ -1276,22 +1276,22 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>8700</v>
+        <v>8600</v>
       </c>
       <c r="E22" s="3">
-        <v>11600</v>
+        <v>11500</v>
       </c>
       <c r="F22" s="3">
-        <v>10300</v>
+        <v>10200</v>
       </c>
       <c r="G22" s="3">
-        <v>11000</v>
+        <v>10900</v>
       </c>
       <c r="H22" s="3">
         <v>10900</v>
       </c>
       <c r="I22" s="3">
-        <v>7900</v>
+        <v>7800</v>
       </c>
       <c r="J22" s="3">
         <v>0</v>
@@ -1321,25 +1321,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>368700</v>
+        <v>366500</v>
       </c>
       <c r="E23" s="3">
-        <v>282400</v>
+        <v>280600</v>
       </c>
       <c r="F23" s="3">
-        <v>-291300</v>
+        <v>-289500</v>
       </c>
       <c r="G23" s="3">
-        <v>403000</v>
+        <v>400500</v>
       </c>
       <c r="H23" s="3">
-        <v>537700</v>
+        <v>534400</v>
       </c>
       <c r="I23" s="3">
-        <v>478200</v>
+        <v>475200</v>
       </c>
       <c r="J23" s="3">
-        <v>354500</v>
+        <v>352300</v>
       </c>
       <c r="K23" s="3">
         <v>20300</v>
@@ -1366,25 +1366,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>87600</v>
+        <v>87000</v>
       </c>
       <c r="E24" s="3">
-        <v>78200</v>
+        <v>77700</v>
       </c>
       <c r="F24" s="3">
-        <v>114400</v>
+        <v>113600</v>
       </c>
       <c r="G24" s="3">
-        <v>105000</v>
+        <v>104400</v>
       </c>
       <c r="H24" s="3">
-        <v>122900</v>
+        <v>122100</v>
       </c>
       <c r="I24" s="3">
-        <v>97300</v>
+        <v>96700</v>
       </c>
       <c r="J24" s="3">
-        <v>61900</v>
+        <v>61500</v>
       </c>
       <c r="K24" s="3">
         <v>700</v>
@@ -1456,25 +1456,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>281100</v>
+        <v>279400</v>
       </c>
       <c r="E26" s="3">
-        <v>204200</v>
+        <v>202900</v>
       </c>
       <c r="F26" s="3">
-        <v>-405600</v>
+        <v>-403100</v>
       </c>
       <c r="G26" s="3">
-        <v>297900</v>
+        <v>296100</v>
       </c>
       <c r="H26" s="3">
-        <v>414900</v>
+        <v>412300</v>
       </c>
       <c r="I26" s="3">
-        <v>380900</v>
+        <v>378500</v>
       </c>
       <c r="J26" s="3">
-        <v>292600</v>
+        <v>290800</v>
       </c>
       <c r="K26" s="3">
         <v>19600</v>
@@ -1501,25 +1501,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>272100</v>
+        <v>270500</v>
       </c>
       <c r="E27" s="3">
-        <v>206300</v>
+        <v>205100</v>
       </c>
       <c r="F27" s="3">
-        <v>-405100</v>
+        <v>-402600</v>
       </c>
       <c r="G27" s="3">
-        <v>292400</v>
+        <v>290600</v>
       </c>
       <c r="H27" s="3">
-        <v>413000</v>
+        <v>410500</v>
       </c>
       <c r="I27" s="3">
-        <v>391400</v>
+        <v>389000</v>
       </c>
       <c r="J27" s="3">
-        <v>298600</v>
+        <v>296800</v>
       </c>
       <c r="K27" s="3">
         <v>19600</v>
@@ -1726,25 +1726,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-75000</v>
+        <v>-60300</v>
       </c>
       <c r="E32" s="3">
-        <v>-51300</v>
+        <v>-51000</v>
       </c>
       <c r="F32" s="3">
-        <v>-53400</v>
+        <v>-53100</v>
       </c>
       <c r="G32" s="3">
-        <v>-61800</v>
+        <v>-61400</v>
       </c>
       <c r="H32" s="3">
-        <v>-56700</v>
+        <v>-56300</v>
       </c>
       <c r="I32" s="3">
-        <v>-37900</v>
+        <v>-37700</v>
       </c>
       <c r="J32" s="3">
-        <v>-20200</v>
+        <v>-20100</v>
       </c>
       <c r="K32" s="3">
         <v>-1100</v>
@@ -1771,25 +1771,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>272100</v>
+        <v>270500</v>
       </c>
       <c r="E33" s="3">
-        <v>206300</v>
+        <v>205100</v>
       </c>
       <c r="F33" s="3">
-        <v>-405100</v>
+        <v>-402600</v>
       </c>
       <c r="G33" s="3">
-        <v>292400</v>
+        <v>290600</v>
       </c>
       <c r="H33" s="3">
-        <v>413000</v>
+        <v>410500</v>
       </c>
       <c r="I33" s="3">
-        <v>391400</v>
+        <v>389000</v>
       </c>
       <c r="J33" s="3">
-        <v>298600</v>
+        <v>296800</v>
       </c>
       <c r="K33" s="3">
         <v>19600</v>
@@ -1861,25 +1861,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>272100</v>
+        <v>270500</v>
       </c>
       <c r="E35" s="3">
-        <v>206300</v>
+        <v>205100</v>
       </c>
       <c r="F35" s="3">
-        <v>-405100</v>
+        <v>-402600</v>
       </c>
       <c r="G35" s="3">
-        <v>292400</v>
+        <v>290600</v>
       </c>
       <c r="H35" s="3">
-        <v>413000</v>
+        <v>410500</v>
       </c>
       <c r="I35" s="3">
-        <v>391400</v>
+        <v>389000</v>
       </c>
       <c r="J35" s="3">
-        <v>298600</v>
+        <v>296800</v>
       </c>
       <c r="K35" s="3">
         <v>19600</v>
@@ -1994,25 +1994,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>781400</v>
+        <v>776500</v>
       </c>
       <c r="E41" s="3">
-        <v>697600</v>
+        <v>693300</v>
       </c>
       <c r="F41" s="3">
-        <v>774400</v>
+        <v>769600</v>
       </c>
       <c r="G41" s="3">
-        <v>467700</v>
+        <v>464800</v>
       </c>
       <c r="H41" s="3">
-        <v>363200</v>
+        <v>361000</v>
       </c>
       <c r="I41" s="3">
-        <v>343100</v>
+        <v>341000</v>
       </c>
       <c r="J41" s="3">
-        <v>620300</v>
+        <v>616500</v>
       </c>
       <c r="K41" s="3">
         <v>35600</v>
@@ -2039,25 +2039,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>176600</v>
+        <v>175500</v>
       </c>
       <c r="E42" s="3">
-        <v>778500</v>
+        <v>773700</v>
       </c>
       <c r="F42" s="3">
-        <v>397600</v>
+        <v>395100</v>
       </c>
       <c r="G42" s="3">
-        <v>1051900</v>
+        <v>1045400</v>
       </c>
       <c r="H42" s="3">
-        <v>1711700</v>
+        <v>1701100</v>
       </c>
       <c r="I42" s="3">
-        <v>1226800</v>
+        <v>1219200</v>
       </c>
       <c r="J42" s="3">
-        <v>339600</v>
+        <v>337500</v>
       </c>
       <c r="K42" s="3">
         <v>54400</v>
@@ -2084,25 +2084,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>29000</v>
+        <v>107900</v>
       </c>
       <c r="E43" s="3">
-        <v>116300</v>
+        <v>115600</v>
       </c>
       <c r="F43" s="3">
-        <v>111500</v>
+        <v>110800</v>
       </c>
       <c r="G43" s="3">
-        <v>83400</v>
+        <v>82900</v>
       </c>
       <c r="H43" s="3">
-        <v>72700</v>
+        <v>72200</v>
       </c>
       <c r="I43" s="3">
-        <v>121700</v>
+        <v>121000</v>
       </c>
       <c r="J43" s="3">
-        <v>57000</v>
+        <v>56600</v>
       </c>
       <c r="K43" s="3">
         <v>6100</v>
@@ -2174,25 +2174,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>102000</v>
+        <v>22300</v>
       </c>
       <c r="E45" s="3">
-        <v>37500</v>
+        <v>37200</v>
       </c>
       <c r="F45" s="3">
-        <v>24800</v>
+        <v>24600</v>
       </c>
       <c r="G45" s="3">
-        <v>30100</v>
+        <v>29900</v>
       </c>
       <c r="H45" s="3">
-        <v>48100</v>
+        <v>47800</v>
       </c>
       <c r="I45" s="3">
-        <v>64600</v>
+        <v>64200</v>
       </c>
       <c r="J45" s="3">
-        <v>63800</v>
+        <v>63400</v>
       </c>
       <c r="K45" s="3">
         <v>3400</v>
@@ -2219,25 +2219,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>1089000</v>
+        <v>1082300</v>
       </c>
       <c r="E46" s="3">
-        <v>1629900</v>
+        <v>1619900</v>
       </c>
       <c r="F46" s="3">
-        <v>1308300</v>
+        <v>1300200</v>
       </c>
       <c r="G46" s="3">
-        <v>1633000</v>
+        <v>1622900</v>
       </c>
       <c r="H46" s="3">
-        <v>2195700</v>
+        <v>2182100</v>
       </c>
       <c r="I46" s="3">
-        <v>1756300</v>
+        <v>1745400</v>
       </c>
       <c r="J46" s="3">
-        <v>1075200</v>
+        <v>1068500</v>
       </c>
       <c r="K46" s="3">
         <v>99400</v>
@@ -2264,25 +2264,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>112200</v>
+        <v>111500</v>
       </c>
       <c r="E47" s="3">
-        <v>124300</v>
+        <v>123500</v>
       </c>
       <c r="F47" s="3">
-        <v>114000</v>
+        <v>113300</v>
       </c>
       <c r="G47" s="3">
-        <v>63300</v>
+        <v>62900</v>
       </c>
       <c r="H47" s="3">
-        <v>68900</v>
+        <v>68500</v>
       </c>
       <c r="I47" s="3">
-        <v>62200</v>
+        <v>61800</v>
       </c>
       <c r="J47" s="3">
-        <v>40100</v>
+        <v>39900</v>
       </c>
       <c r="K47" s="3">
         <v>4400</v>
@@ -2309,25 +2309,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>106900</v>
+        <v>106200</v>
       </c>
       <c r="E48" s="3">
-        <v>40100</v>
+        <v>39900</v>
       </c>
       <c r="F48" s="3">
-        <v>61000</v>
+        <v>60600</v>
       </c>
       <c r="G48" s="3">
-        <v>75600</v>
+        <v>75200</v>
       </c>
       <c r="H48" s="3">
-        <v>74600</v>
+        <v>74200</v>
       </c>
       <c r="I48" s="3">
-        <v>53900</v>
+        <v>53500</v>
       </c>
       <c r="J48" s="3">
-        <v>36000</v>
+        <v>35700</v>
       </c>
       <c r="K48" s="3">
         <v>1900</v>
@@ -2363,13 +2363,13 @@
         <v>3800</v>
       </c>
       <c r="G49" s="3">
-        <v>663900</v>
+        <v>659800</v>
       </c>
       <c r="H49" s="3">
-        <v>730000</v>
+        <v>725500</v>
       </c>
       <c r="I49" s="3">
-        <v>742900</v>
+        <v>738300</v>
       </c>
       <c r="J49" s="3">
         <v>9800</v>
@@ -2489,25 +2489,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>945600</v>
+        <v>939800</v>
       </c>
       <c r="E52" s="3">
-        <v>403200</v>
+        <v>400700</v>
       </c>
       <c r="F52" s="3">
-        <v>1030800</v>
+        <v>1024400</v>
       </c>
       <c r="G52" s="3">
-        <v>792300</v>
+        <v>787400</v>
       </c>
       <c r="H52" s="3">
-        <v>56500</v>
+        <v>56100</v>
       </c>
       <c r="I52" s="3">
-        <v>21300</v>
+        <v>21200</v>
       </c>
       <c r="J52" s="3">
-        <v>16600</v>
+        <v>16500</v>
       </c>
       <c r="K52" s="3">
         <v>500</v>
@@ -2579,25 +2579,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>2256000</v>
+        <v>2242100</v>
       </c>
       <c r="E54" s="3">
-        <v>2200600</v>
+        <v>2187000</v>
       </c>
       <c r="F54" s="3">
-        <v>2517800</v>
+        <v>2502200</v>
       </c>
       <c r="G54" s="3">
-        <v>3228100</v>
+        <v>3208200</v>
       </c>
       <c r="H54" s="3">
-        <v>3125700</v>
+        <v>3106300</v>
       </c>
       <c r="I54" s="3">
-        <v>2636600</v>
+        <v>2620300</v>
       </c>
       <c r="J54" s="3">
-        <v>1177700</v>
+        <v>1170400</v>
       </c>
       <c r="K54" s="3">
         <v>106300</v>
@@ -2662,25 +2662,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>85700</v>
+        <v>85200</v>
       </c>
       <c r="E57" s="3">
-        <v>85800</v>
+        <v>85200</v>
       </c>
       <c r="F57" s="3">
-        <v>101000</v>
+        <v>100300</v>
       </c>
       <c r="G57" s="3">
-        <v>97200</v>
+        <v>96600</v>
       </c>
       <c r="H57" s="3">
-        <v>99300</v>
+        <v>98700</v>
       </c>
       <c r="I57" s="3">
-        <v>99900</v>
+        <v>99200</v>
       </c>
       <c r="J57" s="3">
-        <v>67400</v>
+        <v>67000</v>
       </c>
       <c r="K57" s="3">
         <v>5600</v>
@@ -2707,10 +2707,10 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>30000</v>
+        <v>29800</v>
       </c>
       <c r="E58" s="3">
-        <v>367900</v>
+        <v>365600</v>
       </c>
       <c r="F58" s="3" t="s">
         <v>3</v>
@@ -2752,25 +2752,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>175100</v>
+        <v>174000</v>
       </c>
       <c r="E59" s="3">
-        <v>205100</v>
+        <v>203800</v>
       </c>
       <c r="F59" s="3">
-        <v>248800</v>
+        <v>247200</v>
       </c>
       <c r="G59" s="3">
-        <v>252600</v>
+        <v>251100</v>
       </c>
       <c r="H59" s="3">
-        <v>263100</v>
+        <v>261500</v>
       </c>
       <c r="I59" s="3">
-        <v>275000</v>
+        <v>273300</v>
       </c>
       <c r="J59" s="3">
-        <v>167800</v>
+        <v>166800</v>
       </c>
       <c r="K59" s="3">
         <v>12900</v>
@@ -2797,25 +2797,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>290800</v>
+        <v>289000</v>
       </c>
       <c r="E60" s="3">
-        <v>658700</v>
+        <v>654600</v>
       </c>
       <c r="F60" s="3">
-        <v>349700</v>
+        <v>347600</v>
       </c>
       <c r="G60" s="3">
-        <v>349900</v>
+        <v>347700</v>
       </c>
       <c r="H60" s="3">
-        <v>362400</v>
+        <v>360100</v>
       </c>
       <c r="I60" s="3">
-        <v>374800</v>
+        <v>372500</v>
       </c>
       <c r="J60" s="3">
-        <v>235200</v>
+        <v>233800</v>
       </c>
       <c r="K60" s="3">
         <v>18500</v>
@@ -2842,22 +2842,22 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>272200</v>
+        <v>270500</v>
       </c>
       <c r="E61" s="3">
         <v>0</v>
       </c>
       <c r="F61" s="3">
-        <v>634700</v>
+        <v>630700</v>
       </c>
       <c r="G61" s="3">
-        <v>647700</v>
+        <v>643700</v>
       </c>
       <c r="H61" s="3">
-        <v>688800</v>
+        <v>684500</v>
       </c>
       <c r="I61" s="3">
-        <v>678000</v>
+        <v>673800</v>
       </c>
       <c r="J61" s="3">
         <v>0</v>
@@ -2887,25 +2887,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>26600</v>
+        <v>26400</v>
       </c>
       <c r="E62" s="3">
-        <v>22300</v>
+        <v>22200</v>
       </c>
       <c r="F62" s="3">
-        <v>61800</v>
+        <v>61400</v>
       </c>
       <c r="G62" s="3">
-        <v>168100</v>
+        <v>167100</v>
       </c>
       <c r="H62" s="3">
-        <v>167400</v>
+        <v>166300</v>
       </c>
       <c r="I62" s="3">
-        <v>51300</v>
+        <v>51000</v>
       </c>
       <c r="J62" s="3">
-        <v>3800</v>
+        <v>3700</v>
       </c>
       <c r="K62" s="3">
         <v>300</v>
@@ -3067,25 +3067,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>589600</v>
+        <v>611100</v>
       </c>
       <c r="E66" s="3">
-        <v>702400</v>
+        <v>698000</v>
       </c>
       <c r="F66" s="3">
-        <v>1065500</v>
+        <v>1058900</v>
       </c>
       <c r="G66" s="3">
-        <v>1193000</v>
+        <v>1185600</v>
       </c>
       <c r="H66" s="3">
-        <v>1244700</v>
+        <v>1237000</v>
       </c>
       <c r="I66" s="3">
-        <v>1117000</v>
+        <v>1110100</v>
       </c>
       <c r="J66" s="3">
-        <v>241600</v>
+        <v>240100</v>
       </c>
       <c r="K66" s="3">
         <v>18700</v>
@@ -3310,26 +3310,26 @@
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3" t="s">
-        <v>3</v>
+      <c r="D72" s="3">
+        <v>873200</v>
       </c>
       <c r="E72" s="3">
-        <v>739700</v>
+        <v>735100</v>
       </c>
       <c r="F72" s="3">
-        <v>650300</v>
+        <v>646300</v>
       </c>
       <c r="G72" s="3">
-        <v>1173900</v>
+        <v>1166600</v>
       </c>
       <c r="H72" s="3">
-        <v>1037700</v>
+        <v>1031300</v>
       </c>
       <c r="I72" s="3">
-        <v>745300</v>
+        <v>740700</v>
       </c>
       <c r="J72" s="3">
-        <v>353900</v>
+        <v>351700</v>
       </c>
       <c r="K72" s="3">
         <v>7100</v>
@@ -3491,25 +3491,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>1666400</v>
+        <v>1631000</v>
       </c>
       <c r="E76" s="3">
-        <v>1498300</v>
+        <v>1489000</v>
       </c>
       <c r="F76" s="3">
-        <v>1452300</v>
+        <v>1443300</v>
       </c>
       <c r="G76" s="3">
-        <v>2035100</v>
+        <v>2022500</v>
       </c>
       <c r="H76" s="3">
-        <v>1880900</v>
+        <v>1869300</v>
       </c>
       <c r="I76" s="3">
-        <v>1519600</v>
+        <v>1510200</v>
       </c>
       <c r="J76" s="3">
-        <v>936100</v>
+        <v>930300</v>
       </c>
       <c r="K76" s="3">
         <v>87500</v>
@@ -3631,25 +3631,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>272100</v>
+        <v>270500</v>
       </c>
       <c r="E81" s="3">
-        <v>206300</v>
+        <v>205100</v>
       </c>
       <c r="F81" s="3">
-        <v>-405100</v>
+        <v>-402600</v>
       </c>
       <c r="G81" s="3">
-        <v>292400</v>
+        <v>290600</v>
       </c>
       <c r="H81" s="3">
-        <v>413000</v>
+        <v>410500</v>
       </c>
       <c r="I81" s="3">
-        <v>391400</v>
+        <v>389000</v>
       </c>
       <c r="J81" s="3">
-        <v>298600</v>
+        <v>296800</v>
       </c>
       <c r="K81" s="3">
         <v>19600</v>
@@ -3695,22 +3695,22 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>11100</v>
+        <v>11000</v>
       </c>
       <c r="E83" s="3">
-        <v>15600</v>
+        <v>15500</v>
       </c>
       <c r="F83" s="3">
-        <v>36800</v>
+        <v>36600</v>
       </c>
       <c r="G83" s="3">
-        <v>50900</v>
+        <v>50600</v>
       </c>
       <c r="H83" s="3">
-        <v>49500</v>
+        <v>49200</v>
       </c>
       <c r="I83" s="3">
-        <v>33500</v>
+        <v>33300</v>
       </c>
       <c r="J83" s="3">
         <v>11600</v>
@@ -3965,25 +3965,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>316600</v>
+        <v>314600</v>
       </c>
       <c r="E89" s="3">
-        <v>170600</v>
+        <v>169500</v>
       </c>
       <c r="F89" s="3">
-        <v>216800</v>
+        <v>215400</v>
       </c>
       <c r="G89" s="3">
-        <v>428300</v>
+        <v>425700</v>
       </c>
       <c r="H89" s="3">
-        <v>757500</v>
+        <v>752800</v>
       </c>
       <c r="I89" s="3">
-        <v>462600</v>
+        <v>459800</v>
       </c>
       <c r="J89" s="3">
-        <v>401200</v>
+        <v>398700</v>
       </c>
       <c r="K89" s="3">
         <v>30100</v>
@@ -4029,25 +4029,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-80100</v>
+        <v>-79600</v>
       </c>
       <c r="E91" s="3">
-        <v>-11200</v>
+        <v>-11100</v>
       </c>
       <c r="F91" s="3">
-        <v>-13300</v>
+        <v>-13200</v>
       </c>
       <c r="G91" s="3">
-        <v>-17300</v>
+        <v>-17200</v>
       </c>
       <c r="H91" s="3">
-        <v>-25900</v>
+        <v>-25800</v>
       </c>
       <c r="I91" s="3">
-        <v>-33800</v>
+        <v>-33600</v>
       </c>
       <c r="J91" s="3">
-        <v>-30400</v>
+        <v>-30200</v>
       </c>
       <c r="K91" s="3">
         <v>-1000</v>
@@ -4164,25 +4164,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>335500</v>
+        <v>333400</v>
       </c>
       <c r="E94" s="3">
-        <v>238500</v>
+        <v>237100</v>
       </c>
       <c r="F94" s="3">
-        <v>354500</v>
+        <v>352400</v>
       </c>
       <c r="G94" s="3">
-        <v>-104100</v>
+        <v>-103400</v>
       </c>
       <c r="H94" s="3">
-        <v>-560200</v>
+        <v>-556800</v>
       </c>
       <c r="I94" s="3">
-        <v>-1394900</v>
+        <v>-1386300</v>
       </c>
       <c r="J94" s="3">
-        <v>-26200</v>
+        <v>-26000</v>
       </c>
       <c r="K94" s="3">
         <v>-16300</v>
@@ -4228,19 +4228,19 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-133200</v>
+        <v>-132400</v>
       </c>
       <c r="E96" s="3">
-        <v>-116900</v>
+        <v>-116200</v>
       </c>
       <c r="F96" s="3">
-        <v>-118500</v>
+        <v>-117800</v>
       </c>
       <c r="G96" s="3">
-        <v>-156300</v>
+        <v>-155300</v>
       </c>
       <c r="H96" s="3">
-        <v>-122000</v>
+        <v>-121200</v>
       </c>
       <c r="I96" s="3">
         <v>0</v>
@@ -4408,22 +4408,22 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-236300</v>
+        <v>-234900</v>
       </c>
       <c r="E100" s="3">
-        <v>-477200</v>
+        <v>-474200</v>
       </c>
       <c r="F100" s="3">
-        <v>-248400</v>
+        <v>-246900</v>
       </c>
       <c r="G100" s="3">
-        <v>-208300</v>
+        <v>-207000</v>
       </c>
       <c r="H100" s="3">
-        <v>-177100</v>
+        <v>-176000</v>
       </c>
       <c r="I100" s="3">
-        <v>651700</v>
+        <v>647700</v>
       </c>
       <c r="J100" s="3">
         <v>400</v>
@@ -4453,22 +4453,22 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>13100</v>
+        <v>13000</v>
       </c>
       <c r="E101" s="3">
-        <v>5800</v>
+        <v>5700</v>
       </c>
       <c r="F101" s="3">
         <v>-5800</v>
       </c>
       <c r="G101" s="3">
-        <v>-11300</v>
+        <v>-11200</v>
       </c>
       <c r="H101" s="3">
         <v>-100</v>
       </c>
       <c r="I101" s="3">
-        <v>3400</v>
+        <v>3300</v>
       </c>
       <c r="J101" s="3">
         <v>-3700</v>
@@ -4498,25 +4498,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>428800</v>
+        <v>426100</v>
       </c>
       <c r="E102" s="3">
-        <v>-62300</v>
+        <v>-62000</v>
       </c>
       <c r="F102" s="3">
-        <v>317100</v>
+        <v>315100</v>
       </c>
       <c r="G102" s="3">
-        <v>104700</v>
+        <v>104100</v>
       </c>
       <c r="H102" s="3">
-        <v>20100</v>
+        <v>20000</v>
       </c>
       <c r="I102" s="3">
-        <v>-277200</v>
+        <v>-275500</v>
       </c>
       <c r="J102" s="3">
-        <v>371700</v>
+        <v>369400</v>
       </c>
       <c r="K102" s="3">
         <v>12200</v>

--- a/AAII_Financials/Yearly/MOMO_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/MOMO_YR_FIN.xlsx
@@ -727,25 +727,25 @@
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>1658200</v>
+        <v>1692100</v>
       </c>
       <c r="E8" s="3">
-        <v>1755200</v>
+        <v>1791000</v>
       </c>
       <c r="F8" s="3">
-        <v>2013800</v>
+        <v>2054900</v>
       </c>
       <c r="G8" s="3">
-        <v>2075700</v>
+        <v>2118100</v>
       </c>
       <c r="H8" s="3">
-        <v>2350800</v>
+        <v>2398800</v>
       </c>
       <c r="I8" s="3">
-        <v>1852500</v>
+        <v>1890300</v>
       </c>
       <c r="J8" s="3">
-        <v>1227700</v>
+        <v>1252800</v>
       </c>
       <c r="K8" s="3">
         <v>76400</v>
@@ -772,25 +772,25 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>970600</v>
+        <v>990400</v>
       </c>
       <c r="E9" s="3">
-        <v>1025300</v>
+        <v>1046300</v>
       </c>
       <c r="F9" s="3">
-        <v>1158300</v>
+        <v>1181900</v>
       </c>
       <c r="G9" s="3">
-        <v>1102100</v>
+        <v>1124600</v>
       </c>
       <c r="H9" s="3">
-        <v>1173300</v>
+        <v>1197200</v>
       </c>
       <c r="I9" s="3">
-        <v>992400</v>
+        <v>1012600</v>
       </c>
       <c r="J9" s="3">
-        <v>604200</v>
+        <v>616600</v>
       </c>
       <c r="K9" s="3">
         <v>33300</v>
@@ -817,25 +817,25 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>687600</v>
+        <v>701600</v>
       </c>
       <c r="E10" s="3">
-        <v>729900</v>
+        <v>744800</v>
       </c>
       <c r="F10" s="3">
-        <v>855500</v>
+        <v>873000</v>
       </c>
       <c r="G10" s="3">
-        <v>973700</v>
+        <v>993500</v>
       </c>
       <c r="H10" s="3">
-        <v>1177500</v>
+        <v>1201600</v>
       </c>
       <c r="I10" s="3">
-        <v>860100</v>
+        <v>877700</v>
       </c>
       <c r="J10" s="3">
-        <v>623500</v>
+        <v>636200</v>
       </c>
       <c r="K10" s="3">
         <v>43000</v>
@@ -881,25 +881,25 @@
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>122200</v>
+        <v>124700</v>
       </c>
       <c r="E12" s="3">
-        <v>139000</v>
+        <v>141900</v>
       </c>
       <c r="F12" s="3">
-        <v>156400</v>
+        <v>159600</v>
       </c>
       <c r="G12" s="3">
-        <v>161300</v>
+        <v>164600</v>
       </c>
       <c r="H12" s="3">
-        <v>151300</v>
+        <v>154400</v>
       </c>
       <c r="I12" s="3">
-        <v>105100</v>
+        <v>107200</v>
       </c>
       <c r="J12" s="3">
-        <v>47800</v>
+        <v>48800</v>
       </c>
       <c r="K12" s="3">
         <v>4300</v>
@@ -971,13 +971,13 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>3700</v>
+        <v>3800</v>
       </c>
       <c r="E14" s="3">
-        <v>-16300</v>
+        <v>-16700</v>
       </c>
       <c r="F14" s="3">
-        <v>609700</v>
+        <v>622100</v>
       </c>
       <c r="G14" s="3">
         <v>-200</v>
@@ -986,7 +986,7 @@
         <v>2200</v>
       </c>
       <c r="I14" s="3">
-        <v>6000</v>
+        <v>6100</v>
       </c>
       <c r="J14" s="3">
         <v>4200</v>
@@ -1077,25 +1077,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1343500</v>
+        <v>1370900</v>
       </c>
       <c r="E17" s="3">
-        <v>1514000</v>
+        <v>1544900</v>
       </c>
       <c r="F17" s="3">
-        <v>2346100</v>
+        <v>2394000</v>
       </c>
       <c r="G17" s="3">
-        <v>1725800</v>
+        <v>1761000</v>
       </c>
       <c r="H17" s="3">
-        <v>1861900</v>
+        <v>1899900</v>
       </c>
       <c r="I17" s="3">
-        <v>1407200</v>
+        <v>1435900</v>
       </c>
       <c r="J17" s="3">
-        <v>895600</v>
+        <v>913900</v>
       </c>
       <c r="K17" s="3">
         <v>57200</v>
@@ -1122,25 +1122,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>314800</v>
+        <v>321200</v>
       </c>
       <c r="E18" s="3">
-        <v>241200</v>
+        <v>246100</v>
       </c>
       <c r="F18" s="3">
-        <v>-332400</v>
+        <v>-339100</v>
       </c>
       <c r="G18" s="3">
-        <v>350000</v>
+        <v>357100</v>
       </c>
       <c r="H18" s="3">
-        <v>488900</v>
+        <v>498900</v>
       </c>
       <c r="I18" s="3">
-        <v>445300</v>
+        <v>454400</v>
       </c>
       <c r="J18" s="3">
-        <v>332200</v>
+        <v>338900</v>
       </c>
       <c r="K18" s="3">
         <v>19200</v>
@@ -1186,25 +1186,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>60300</v>
+        <v>61500</v>
       </c>
       <c r="E20" s="3">
-        <v>51000</v>
+        <v>52000</v>
       </c>
       <c r="F20" s="3">
-        <v>53100</v>
+        <v>54200</v>
       </c>
       <c r="G20" s="3">
-        <v>61400</v>
+        <v>62700</v>
       </c>
       <c r="H20" s="3">
-        <v>56300</v>
+        <v>57500</v>
       </c>
       <c r="I20" s="3">
-        <v>37700</v>
+        <v>38500</v>
       </c>
       <c r="J20" s="3">
-        <v>20100</v>
+        <v>20500</v>
       </c>
       <c r="K20" s="3">
         <v>1100</v>
@@ -1231,25 +1231,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>386000</v>
+        <v>393900</v>
       </c>
       <c r="E21" s="3">
-        <v>307600</v>
+        <v>313900</v>
       </c>
       <c r="F21" s="3">
-        <v>-242800</v>
+        <v>-247800</v>
       </c>
       <c r="G21" s="3">
-        <v>461800</v>
+        <v>471200</v>
       </c>
       <c r="H21" s="3">
-        <v>594400</v>
+        <v>606400</v>
       </c>
       <c r="I21" s="3">
-        <v>516300</v>
+        <v>526800</v>
       </c>
       <c r="J21" s="3">
-        <v>363800</v>
+        <v>371200</v>
       </c>
       <c r="K21" s="3">
         <v>21400</v>
@@ -1276,22 +1276,22 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>8600</v>
+        <v>8800</v>
       </c>
       <c r="E22" s="3">
-        <v>11500</v>
+        <v>11800</v>
       </c>
       <c r="F22" s="3">
-        <v>10200</v>
+        <v>10400</v>
       </c>
       <c r="G22" s="3">
-        <v>10900</v>
+        <v>11100</v>
       </c>
       <c r="H22" s="3">
-        <v>10900</v>
+        <v>11100</v>
       </c>
       <c r="I22" s="3">
-        <v>7800</v>
+        <v>8000</v>
       </c>
       <c r="J22" s="3">
         <v>0</v>
@@ -1321,25 +1321,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>366500</v>
+        <v>373900</v>
       </c>
       <c r="E23" s="3">
-        <v>280600</v>
+        <v>286400</v>
       </c>
       <c r="F23" s="3">
-        <v>-289500</v>
+        <v>-295400</v>
       </c>
       <c r="G23" s="3">
-        <v>400500</v>
+        <v>408600</v>
       </c>
       <c r="H23" s="3">
-        <v>534400</v>
+        <v>545300</v>
       </c>
       <c r="I23" s="3">
-        <v>475200</v>
+        <v>484900</v>
       </c>
       <c r="J23" s="3">
-        <v>352300</v>
+        <v>359500</v>
       </c>
       <c r="K23" s="3">
         <v>20300</v>
@@ -1366,25 +1366,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>87000</v>
+        <v>88800</v>
       </c>
       <c r="E24" s="3">
-        <v>77700</v>
+        <v>79300</v>
       </c>
       <c r="F24" s="3">
-        <v>113600</v>
+        <v>116000</v>
       </c>
       <c r="G24" s="3">
-        <v>104400</v>
+        <v>106500</v>
       </c>
       <c r="H24" s="3">
-        <v>122100</v>
+        <v>124600</v>
       </c>
       <c r="I24" s="3">
-        <v>96700</v>
+        <v>98600</v>
       </c>
       <c r="J24" s="3">
-        <v>61500</v>
+        <v>62700</v>
       </c>
       <c r="K24" s="3">
         <v>700</v>
@@ -1456,25 +1456,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>279400</v>
+        <v>285100</v>
       </c>
       <c r="E26" s="3">
-        <v>202900</v>
+        <v>207100</v>
       </c>
       <c r="F26" s="3">
-        <v>-403100</v>
+        <v>-411300</v>
       </c>
       <c r="G26" s="3">
-        <v>296100</v>
+        <v>302100</v>
       </c>
       <c r="H26" s="3">
-        <v>412300</v>
+        <v>420700</v>
       </c>
       <c r="I26" s="3">
-        <v>378500</v>
+        <v>386300</v>
       </c>
       <c r="J26" s="3">
-        <v>290800</v>
+        <v>296700</v>
       </c>
       <c r="K26" s="3">
         <v>19600</v>
@@ -1501,25 +1501,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>270500</v>
+        <v>276000</v>
       </c>
       <c r="E27" s="3">
-        <v>205100</v>
+        <v>209300</v>
       </c>
       <c r="F27" s="3">
-        <v>-402600</v>
+        <v>-410800</v>
       </c>
       <c r="G27" s="3">
-        <v>290600</v>
+        <v>296500</v>
       </c>
       <c r="H27" s="3">
-        <v>410500</v>
+        <v>418800</v>
       </c>
       <c r="I27" s="3">
-        <v>389000</v>
+        <v>397000</v>
       </c>
       <c r="J27" s="3">
-        <v>296800</v>
+        <v>302800</v>
       </c>
       <c r="K27" s="3">
         <v>19600</v>
@@ -1726,25 +1726,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-60300</v>
+        <v>-61500</v>
       </c>
       <c r="E32" s="3">
-        <v>-51000</v>
+        <v>-52000</v>
       </c>
       <c r="F32" s="3">
-        <v>-53100</v>
+        <v>-54200</v>
       </c>
       <c r="G32" s="3">
-        <v>-61400</v>
+        <v>-62700</v>
       </c>
       <c r="H32" s="3">
-        <v>-56300</v>
+        <v>-57500</v>
       </c>
       <c r="I32" s="3">
-        <v>-37700</v>
+        <v>-38500</v>
       </c>
       <c r="J32" s="3">
-        <v>-20100</v>
+        <v>-20500</v>
       </c>
       <c r="K32" s="3">
         <v>-1100</v>
@@ -1771,25 +1771,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>270500</v>
+        <v>276000</v>
       </c>
       <c r="E33" s="3">
-        <v>205100</v>
+        <v>209300</v>
       </c>
       <c r="F33" s="3">
-        <v>-402600</v>
+        <v>-410800</v>
       </c>
       <c r="G33" s="3">
-        <v>290600</v>
+        <v>296500</v>
       </c>
       <c r="H33" s="3">
-        <v>410500</v>
+        <v>418800</v>
       </c>
       <c r="I33" s="3">
-        <v>389000</v>
+        <v>397000</v>
       </c>
       <c r="J33" s="3">
-        <v>296800</v>
+        <v>302800</v>
       </c>
       <c r="K33" s="3">
         <v>19600</v>
@@ -1861,25 +1861,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>270500</v>
+        <v>276000</v>
       </c>
       <c r="E35" s="3">
-        <v>205100</v>
+        <v>209300</v>
       </c>
       <c r="F35" s="3">
-        <v>-402600</v>
+        <v>-410800</v>
       </c>
       <c r="G35" s="3">
-        <v>290600</v>
+        <v>296500</v>
       </c>
       <c r="H35" s="3">
-        <v>410500</v>
+        <v>418800</v>
       </c>
       <c r="I35" s="3">
-        <v>389000</v>
+        <v>397000</v>
       </c>
       <c r="J35" s="3">
-        <v>296800</v>
+        <v>302800</v>
       </c>
       <c r="K35" s="3">
         <v>19600</v>
@@ -1994,25 +1994,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>776500</v>
+        <v>792400</v>
       </c>
       <c r="E41" s="3">
-        <v>693300</v>
+        <v>707500</v>
       </c>
       <c r="F41" s="3">
-        <v>769600</v>
+        <v>785300</v>
       </c>
       <c r="G41" s="3">
-        <v>464800</v>
+        <v>474200</v>
       </c>
       <c r="H41" s="3">
-        <v>361000</v>
+        <v>368300</v>
       </c>
       <c r="I41" s="3">
-        <v>341000</v>
+        <v>347900</v>
       </c>
       <c r="J41" s="3">
-        <v>616500</v>
+        <v>629100</v>
       </c>
       <c r="K41" s="3">
         <v>35600</v>
@@ -2039,25 +2039,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>175500</v>
+        <v>179100</v>
       </c>
       <c r="E42" s="3">
-        <v>773700</v>
+        <v>789500</v>
       </c>
       <c r="F42" s="3">
-        <v>395100</v>
+        <v>403200</v>
       </c>
       <c r="G42" s="3">
-        <v>1045400</v>
+        <v>1066700</v>
       </c>
       <c r="H42" s="3">
-        <v>1701100</v>
+        <v>1735800</v>
       </c>
       <c r="I42" s="3">
-        <v>1219200</v>
+        <v>1244100</v>
       </c>
       <c r="J42" s="3">
-        <v>337500</v>
+        <v>344300</v>
       </c>
       <c r="K42" s="3">
         <v>54400</v>
@@ -2084,25 +2084,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>107900</v>
+        <v>110100</v>
       </c>
       <c r="E43" s="3">
-        <v>115600</v>
+        <v>118000</v>
       </c>
       <c r="F43" s="3">
-        <v>110800</v>
+        <v>113100</v>
       </c>
       <c r="G43" s="3">
-        <v>82900</v>
+        <v>84600</v>
       </c>
       <c r="H43" s="3">
-        <v>72200</v>
+        <v>73700</v>
       </c>
       <c r="I43" s="3">
-        <v>121000</v>
+        <v>123500</v>
       </c>
       <c r="J43" s="3">
-        <v>56600</v>
+        <v>57800</v>
       </c>
       <c r="K43" s="3">
         <v>6100</v>
@@ -2174,25 +2174,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>22300</v>
+        <v>22700</v>
       </c>
       <c r="E45" s="3">
-        <v>37200</v>
+        <v>38000</v>
       </c>
       <c r="F45" s="3">
-        <v>24600</v>
+        <v>25100</v>
       </c>
       <c r="G45" s="3">
-        <v>29900</v>
+        <v>30500</v>
       </c>
       <c r="H45" s="3">
-        <v>47800</v>
+        <v>48700</v>
       </c>
       <c r="I45" s="3">
-        <v>64200</v>
+        <v>65500</v>
       </c>
       <c r="J45" s="3">
-        <v>63400</v>
+        <v>64700</v>
       </c>
       <c r="K45" s="3">
         <v>3400</v>
@@ -2219,25 +2219,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>1082300</v>
+        <v>1104300</v>
       </c>
       <c r="E46" s="3">
-        <v>1619900</v>
+        <v>1652900</v>
       </c>
       <c r="F46" s="3">
-        <v>1300200</v>
+        <v>1326700</v>
       </c>
       <c r="G46" s="3">
-        <v>1622900</v>
+        <v>1656100</v>
       </c>
       <c r="H46" s="3">
-        <v>2182100</v>
+        <v>2226600</v>
       </c>
       <c r="I46" s="3">
-        <v>1745400</v>
+        <v>1781000</v>
       </c>
       <c r="J46" s="3">
-        <v>1068500</v>
+        <v>1090300</v>
       </c>
       <c r="K46" s="3">
         <v>99400</v>
@@ -2264,25 +2264,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>111500</v>
+        <v>113800</v>
       </c>
       <c r="E47" s="3">
-        <v>123500</v>
+        <v>126000</v>
       </c>
       <c r="F47" s="3">
-        <v>113300</v>
+        <v>115600</v>
       </c>
       <c r="G47" s="3">
-        <v>62900</v>
+        <v>64100</v>
       </c>
       <c r="H47" s="3">
-        <v>68500</v>
+        <v>69900</v>
       </c>
       <c r="I47" s="3">
-        <v>61800</v>
+        <v>63100</v>
       </c>
       <c r="J47" s="3">
-        <v>39900</v>
+        <v>40700</v>
       </c>
       <c r="K47" s="3">
         <v>4400</v>
@@ -2309,25 +2309,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>106200</v>
+        <v>108400</v>
       </c>
       <c r="E48" s="3">
-        <v>39900</v>
+        <v>40700</v>
       </c>
       <c r="F48" s="3">
-        <v>60600</v>
+        <v>61800</v>
       </c>
       <c r="G48" s="3">
-        <v>75200</v>
+        <v>76700</v>
       </c>
       <c r="H48" s="3">
-        <v>74200</v>
+        <v>75700</v>
       </c>
       <c r="I48" s="3">
-        <v>53500</v>
+        <v>54600</v>
       </c>
       <c r="J48" s="3">
-        <v>35700</v>
+        <v>36500</v>
       </c>
       <c r="K48" s="3">
         <v>1900</v>
@@ -2360,19 +2360,19 @@
         <v>3100</v>
       </c>
       <c r="F49" s="3">
-        <v>3800</v>
+        <v>3900</v>
       </c>
       <c r="G49" s="3">
-        <v>659800</v>
+        <v>673300</v>
       </c>
       <c r="H49" s="3">
-        <v>725500</v>
+        <v>740300</v>
       </c>
       <c r="I49" s="3">
-        <v>738300</v>
+        <v>753400</v>
       </c>
       <c r="J49" s="3">
-        <v>9800</v>
+        <v>10000</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>3</v>
@@ -2489,25 +2489,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>939800</v>
+        <v>959000</v>
       </c>
       <c r="E52" s="3">
-        <v>400700</v>
+        <v>408900</v>
       </c>
       <c r="F52" s="3">
-        <v>1024400</v>
+        <v>1045300</v>
       </c>
       <c r="G52" s="3">
-        <v>787400</v>
+        <v>803500</v>
       </c>
       <c r="H52" s="3">
-        <v>56100</v>
+        <v>57300</v>
       </c>
       <c r="I52" s="3">
-        <v>21200</v>
+        <v>21600</v>
       </c>
       <c r="J52" s="3">
-        <v>16500</v>
+        <v>16800</v>
       </c>
       <c r="K52" s="3">
         <v>500</v>
@@ -2579,25 +2579,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>2242100</v>
+        <v>2287800</v>
       </c>
       <c r="E54" s="3">
-        <v>2187000</v>
+        <v>2231700</v>
       </c>
       <c r="F54" s="3">
-        <v>2502200</v>
+        <v>2553300</v>
       </c>
       <c r="G54" s="3">
-        <v>3208200</v>
+        <v>3273600</v>
       </c>
       <c r="H54" s="3">
-        <v>3106300</v>
+        <v>3169700</v>
       </c>
       <c r="I54" s="3">
-        <v>2620300</v>
+        <v>2673800</v>
       </c>
       <c r="J54" s="3">
-        <v>1170400</v>
+        <v>1194300</v>
       </c>
       <c r="K54" s="3">
         <v>106300</v>
@@ -2662,25 +2662,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>85200</v>
+        <v>86900</v>
       </c>
       <c r="E57" s="3">
-        <v>85200</v>
+        <v>87000</v>
       </c>
       <c r="F57" s="3">
-        <v>100300</v>
+        <v>102400</v>
       </c>
       <c r="G57" s="3">
-        <v>96600</v>
+        <v>98600</v>
       </c>
       <c r="H57" s="3">
-        <v>98700</v>
+        <v>100700</v>
       </c>
       <c r="I57" s="3">
-        <v>99200</v>
+        <v>101300</v>
       </c>
       <c r="J57" s="3">
-        <v>67000</v>
+        <v>68400</v>
       </c>
       <c r="K57" s="3">
         <v>5600</v>
@@ -2707,10 +2707,10 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>29800</v>
+        <v>30400</v>
       </c>
       <c r="E58" s="3">
-        <v>365600</v>
+        <v>373100</v>
       </c>
       <c r="F58" s="3" t="s">
         <v>3</v>
@@ -2752,25 +2752,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>174000</v>
+        <v>177600</v>
       </c>
       <c r="E59" s="3">
-        <v>203800</v>
+        <v>208000</v>
       </c>
       <c r="F59" s="3">
-        <v>247200</v>
+        <v>252300</v>
       </c>
       <c r="G59" s="3">
-        <v>251100</v>
+        <v>256200</v>
       </c>
       <c r="H59" s="3">
-        <v>261500</v>
+        <v>266800</v>
       </c>
       <c r="I59" s="3">
-        <v>273300</v>
+        <v>278800</v>
       </c>
       <c r="J59" s="3">
-        <v>166800</v>
+        <v>170200</v>
       </c>
       <c r="K59" s="3">
         <v>12900</v>
@@ -2797,25 +2797,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>289000</v>
+        <v>294900</v>
       </c>
       <c r="E60" s="3">
-        <v>654600</v>
+        <v>668000</v>
       </c>
       <c r="F60" s="3">
-        <v>347600</v>
+        <v>354700</v>
       </c>
       <c r="G60" s="3">
-        <v>347700</v>
+        <v>354800</v>
       </c>
       <c r="H60" s="3">
-        <v>360100</v>
+        <v>367500</v>
       </c>
       <c r="I60" s="3">
-        <v>372500</v>
+        <v>380100</v>
       </c>
       <c r="J60" s="3">
-        <v>233800</v>
+        <v>238500</v>
       </c>
       <c r="K60" s="3">
         <v>18500</v>
@@ -2842,22 +2842,22 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>270500</v>
+        <v>276000</v>
       </c>
       <c r="E61" s="3">
         <v>0</v>
       </c>
       <c r="F61" s="3">
-        <v>630700</v>
+        <v>643600</v>
       </c>
       <c r="G61" s="3">
-        <v>643700</v>
+        <v>656800</v>
       </c>
       <c r="H61" s="3">
-        <v>684500</v>
+        <v>698500</v>
       </c>
       <c r="I61" s="3">
-        <v>673800</v>
+        <v>687600</v>
       </c>
       <c r="J61" s="3">
         <v>0</v>
@@ -2887,25 +2887,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>26400</v>
+        <v>27000</v>
       </c>
       <c r="E62" s="3">
-        <v>22200</v>
+        <v>22700</v>
       </c>
       <c r="F62" s="3">
-        <v>61400</v>
+        <v>62700</v>
       </c>
       <c r="G62" s="3">
-        <v>167100</v>
+        <v>170500</v>
       </c>
       <c r="H62" s="3">
-        <v>166300</v>
+        <v>169700</v>
       </c>
       <c r="I62" s="3">
-        <v>51000</v>
+        <v>52100</v>
       </c>
       <c r="J62" s="3">
-        <v>3700</v>
+        <v>3800</v>
       </c>
       <c r="K62" s="3">
         <v>300</v>
@@ -3067,25 +3067,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>611100</v>
+        <v>623600</v>
       </c>
       <c r="E66" s="3">
-        <v>698000</v>
+        <v>712300</v>
       </c>
       <c r="F66" s="3">
-        <v>1058900</v>
+        <v>1080600</v>
       </c>
       <c r="G66" s="3">
-        <v>1185600</v>
+        <v>1209800</v>
       </c>
       <c r="H66" s="3">
-        <v>1237000</v>
+        <v>1262300</v>
       </c>
       <c r="I66" s="3">
-        <v>1110100</v>
+        <v>1132800</v>
       </c>
       <c r="J66" s="3">
-        <v>240100</v>
+        <v>245000</v>
       </c>
       <c r="K66" s="3">
         <v>18700</v>
@@ -3311,25 +3311,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>873200</v>
+        <v>891100</v>
       </c>
       <c r="E72" s="3">
-        <v>735100</v>
+        <v>750100</v>
       </c>
       <c r="F72" s="3">
-        <v>646300</v>
+        <v>659500</v>
       </c>
       <c r="G72" s="3">
-        <v>1166600</v>
+        <v>1190400</v>
       </c>
       <c r="H72" s="3">
-        <v>1031300</v>
+        <v>1052400</v>
       </c>
       <c r="I72" s="3">
-        <v>740700</v>
+        <v>755800</v>
       </c>
       <c r="J72" s="3">
-        <v>351700</v>
+        <v>358800</v>
       </c>
       <c r="K72" s="3">
         <v>7100</v>
@@ -3491,25 +3491,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>1631000</v>
+        <v>1664300</v>
       </c>
       <c r="E76" s="3">
-        <v>1489000</v>
+        <v>1519400</v>
       </c>
       <c r="F76" s="3">
-        <v>1443300</v>
+        <v>1472800</v>
       </c>
       <c r="G76" s="3">
-        <v>2022500</v>
+        <v>2063800</v>
       </c>
       <c r="H76" s="3">
-        <v>1869300</v>
+        <v>1907500</v>
       </c>
       <c r="I76" s="3">
-        <v>1510200</v>
+        <v>1541000</v>
       </c>
       <c r="J76" s="3">
-        <v>930300</v>
+        <v>949300</v>
       </c>
       <c r="K76" s="3">
         <v>87500</v>
@@ -3631,25 +3631,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>270500</v>
+        <v>276000</v>
       </c>
       <c r="E81" s="3">
-        <v>205100</v>
+        <v>209300</v>
       </c>
       <c r="F81" s="3">
-        <v>-402600</v>
+        <v>-410800</v>
       </c>
       <c r="G81" s="3">
-        <v>290600</v>
+        <v>296500</v>
       </c>
       <c r="H81" s="3">
-        <v>410500</v>
+        <v>418800</v>
       </c>
       <c r="I81" s="3">
-        <v>389000</v>
+        <v>397000</v>
       </c>
       <c r="J81" s="3">
-        <v>296800</v>
+        <v>302800</v>
       </c>
       <c r="K81" s="3">
         <v>19600</v>
@@ -3695,25 +3695,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>11000</v>
+        <v>11200</v>
       </c>
       <c r="E83" s="3">
-        <v>15500</v>
+        <v>15800</v>
       </c>
       <c r="F83" s="3">
-        <v>36600</v>
+        <v>37300</v>
       </c>
       <c r="G83" s="3">
-        <v>50600</v>
+        <v>51600</v>
       </c>
       <c r="H83" s="3">
-        <v>49200</v>
+        <v>50200</v>
       </c>
       <c r="I83" s="3">
-        <v>33300</v>
+        <v>34000</v>
       </c>
       <c r="J83" s="3">
-        <v>11600</v>
+        <v>11800</v>
       </c>
       <c r="K83" s="3">
         <v>1200</v>
@@ -3965,25 +3965,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>314600</v>
+        <v>321000</v>
       </c>
       <c r="E89" s="3">
-        <v>169500</v>
+        <v>173000</v>
       </c>
       <c r="F89" s="3">
-        <v>215400</v>
+        <v>219800</v>
       </c>
       <c r="G89" s="3">
-        <v>425700</v>
+        <v>434300</v>
       </c>
       <c r="H89" s="3">
-        <v>752800</v>
+        <v>768200</v>
       </c>
       <c r="I89" s="3">
-        <v>459800</v>
+        <v>469100</v>
       </c>
       <c r="J89" s="3">
-        <v>398700</v>
+        <v>406900</v>
       </c>
       <c r="K89" s="3">
         <v>30100</v>
@@ -4029,25 +4029,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-79600</v>
+        <v>-81200</v>
       </c>
       <c r="E91" s="3">
-        <v>-11100</v>
+        <v>-11300</v>
       </c>
       <c r="F91" s="3">
-        <v>-13200</v>
+        <v>-13400</v>
       </c>
       <c r="G91" s="3">
-        <v>-17200</v>
+        <v>-17500</v>
       </c>
       <c r="H91" s="3">
-        <v>-25800</v>
+        <v>-26300</v>
       </c>
       <c r="I91" s="3">
-        <v>-33600</v>
+        <v>-34200</v>
       </c>
       <c r="J91" s="3">
-        <v>-30200</v>
+        <v>-30800</v>
       </c>
       <c r="K91" s="3">
         <v>-1000</v>
@@ -4164,25 +4164,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>333400</v>
+        <v>340200</v>
       </c>
       <c r="E94" s="3">
-        <v>237100</v>
+        <v>241900</v>
       </c>
       <c r="F94" s="3">
-        <v>352400</v>
+        <v>359500</v>
       </c>
       <c r="G94" s="3">
-        <v>-103400</v>
+        <v>-105500</v>
       </c>
       <c r="H94" s="3">
-        <v>-556800</v>
+        <v>-568100</v>
       </c>
       <c r="I94" s="3">
-        <v>-1386300</v>
+        <v>-1414600</v>
       </c>
       <c r="J94" s="3">
-        <v>-26000</v>
+        <v>-26500</v>
       </c>
       <c r="K94" s="3">
         <v>-16300</v>
@@ -4228,19 +4228,19 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-132400</v>
+        <v>-135100</v>
       </c>
       <c r="E96" s="3">
-        <v>-116200</v>
+        <v>-118600</v>
       </c>
       <c r="F96" s="3">
-        <v>-117800</v>
+        <v>-120200</v>
       </c>
       <c r="G96" s="3">
-        <v>-155300</v>
+        <v>-158500</v>
       </c>
       <c r="H96" s="3">
-        <v>-121200</v>
+        <v>-123700</v>
       </c>
       <c r="I96" s="3">
         <v>0</v>
@@ -4408,22 +4408,22 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-234900</v>
+        <v>-239700</v>
       </c>
       <c r="E100" s="3">
-        <v>-474200</v>
+        <v>-483900</v>
       </c>
       <c r="F100" s="3">
-        <v>-246900</v>
+        <v>-251900</v>
       </c>
       <c r="G100" s="3">
-        <v>-207000</v>
+        <v>-211200</v>
       </c>
       <c r="H100" s="3">
-        <v>-176000</v>
+        <v>-179600</v>
       </c>
       <c r="I100" s="3">
-        <v>647700</v>
+        <v>660900</v>
       </c>
       <c r="J100" s="3">
         <v>400</v>
@@ -4453,25 +4453,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>13000</v>
+        <v>13300</v>
       </c>
       <c r="E101" s="3">
-        <v>5700</v>
+        <v>5800</v>
       </c>
       <c r="F101" s="3">
-        <v>-5800</v>
+        <v>-5900</v>
       </c>
       <c r="G101" s="3">
-        <v>-11200</v>
+        <v>-11400</v>
       </c>
       <c r="H101" s="3">
         <v>-100</v>
       </c>
       <c r="I101" s="3">
-        <v>3300</v>
+        <v>3400</v>
       </c>
       <c r="J101" s="3">
-        <v>-3700</v>
+        <v>-3800</v>
       </c>
       <c r="K101" s="3">
         <v>-1600</v>
@@ -4498,25 +4498,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>426100</v>
+        <v>434800</v>
       </c>
       <c r="E102" s="3">
-        <v>-62000</v>
+        <v>-63200</v>
       </c>
       <c r="F102" s="3">
-        <v>315100</v>
+        <v>321600</v>
       </c>
       <c r="G102" s="3">
-        <v>104100</v>
+        <v>106200</v>
       </c>
       <c r="H102" s="3">
-        <v>20000</v>
+        <v>20400</v>
       </c>
       <c r="I102" s="3">
-        <v>-275500</v>
+        <v>-281100</v>
       </c>
       <c r="J102" s="3">
-        <v>369400</v>
+        <v>377000</v>
       </c>
       <c r="K102" s="3">
         <v>12200</v>

--- a/AAII_Financials/Yearly/MOMO_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/MOMO_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="92">
   <si>
     <t>MOMO</t>
   </si>
@@ -727,25 +727,25 @@
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>1692100</v>
+        <v>1692600</v>
       </c>
       <c r="E8" s="3">
-        <v>1791000</v>
+        <v>1841900</v>
       </c>
       <c r="F8" s="3">
-        <v>2054900</v>
+        <v>2294400</v>
       </c>
       <c r="G8" s="3">
-        <v>2118100</v>
+        <v>2301300</v>
       </c>
       <c r="H8" s="3">
-        <v>2398800</v>
+        <v>2443700</v>
       </c>
       <c r="I8" s="3">
-        <v>1890300</v>
+        <v>1949600</v>
       </c>
       <c r="J8" s="3">
-        <v>1252800</v>
+        <v>1365700</v>
       </c>
       <c r="K8" s="3">
         <v>76400</v>
@@ -772,25 +772,25 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>990400</v>
+        <v>990800</v>
       </c>
       <c r="E9" s="3">
-        <v>1046300</v>
+        <v>1076000</v>
       </c>
       <c r="F9" s="3">
-        <v>1181900</v>
+        <v>1319700</v>
       </c>
       <c r="G9" s="3">
-        <v>1124600</v>
+        <v>1221800</v>
       </c>
       <c r="H9" s="3">
-        <v>1197200</v>
+        <v>1219600</v>
       </c>
       <c r="I9" s="3">
-        <v>1012600</v>
+        <v>1044400</v>
       </c>
       <c r="J9" s="3">
-        <v>616600</v>
+        <v>672100</v>
       </c>
       <c r="K9" s="3">
         <v>33300</v>
@@ -817,25 +817,25 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>701600</v>
+        <v>701900</v>
       </c>
       <c r="E10" s="3">
-        <v>744800</v>
+        <v>765900</v>
       </c>
       <c r="F10" s="3">
-        <v>873000</v>
+        <v>974800</v>
       </c>
       <c r="G10" s="3">
-        <v>993500</v>
+        <v>1079500</v>
       </c>
       <c r="H10" s="3">
-        <v>1201600</v>
+        <v>1224100</v>
       </c>
       <c r="I10" s="3">
-        <v>877700</v>
+        <v>905200</v>
       </c>
       <c r="J10" s="3">
-        <v>636200</v>
+        <v>693600</v>
       </c>
       <c r="K10" s="3">
         <v>43000</v>
@@ -881,25 +881,25 @@
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>124700</v>
+        <v>124800</v>
       </c>
       <c r="E12" s="3">
-        <v>141900</v>
+        <v>145900</v>
       </c>
       <c r="F12" s="3">
-        <v>159600</v>
+        <v>178200</v>
       </c>
       <c r="G12" s="3">
-        <v>164600</v>
+        <v>178900</v>
       </c>
       <c r="H12" s="3">
-        <v>154400</v>
+        <v>157300</v>
       </c>
       <c r="I12" s="3">
-        <v>107200</v>
+        <v>110600</v>
       </c>
       <c r="J12" s="3">
-        <v>48800</v>
+        <v>53200</v>
       </c>
       <c r="K12" s="3">
         <v>4300</v>
@@ -974,22 +974,22 @@
         <v>3800</v>
       </c>
       <c r="E14" s="3">
-        <v>-16700</v>
+        <v>-17200</v>
       </c>
       <c r="F14" s="3">
-        <v>622100</v>
+        <v>695000</v>
       </c>
       <c r="G14" s="3">
-        <v>-200</v>
+        <v>1600</v>
       </c>
       <c r="H14" s="3">
-        <v>2200</v>
+        <v>2300</v>
       </c>
       <c r="I14" s="3">
-        <v>6100</v>
+        <v>6300</v>
       </c>
       <c r="J14" s="3">
-        <v>4200</v>
+        <v>4600</v>
       </c>
       <c r="K14" s="3">
         <v>800</v>
@@ -1016,25 +1016,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>11200</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>16300</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>41700</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>56100</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>51200</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>35100</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>12900</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1077,25 +1077,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1370900</v>
+        <v>1367600</v>
       </c>
       <c r="E17" s="3">
-        <v>1544900</v>
+        <v>1606000</v>
       </c>
       <c r="F17" s="3">
-        <v>2394000</v>
+        <v>1978400</v>
       </c>
       <c r="G17" s="3">
-        <v>1761000</v>
+        <v>1913500</v>
       </c>
       <c r="H17" s="3">
-        <v>1899900</v>
+        <v>1933200</v>
       </c>
       <c r="I17" s="3">
-        <v>1435900</v>
+        <v>1474600</v>
       </c>
       <c r="J17" s="3">
-        <v>913900</v>
+        <v>991600</v>
       </c>
       <c r="K17" s="3">
         <v>57200</v>
@@ -1122,25 +1122,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>321200</v>
+        <v>325100</v>
       </c>
       <c r="E18" s="3">
-        <v>246100</v>
+        <v>236000</v>
       </c>
       <c r="F18" s="3">
-        <v>-339100</v>
+        <v>316000</v>
       </c>
       <c r="G18" s="3">
-        <v>357100</v>
+        <v>387700</v>
       </c>
       <c r="H18" s="3">
-        <v>498900</v>
+        <v>510500</v>
       </c>
       <c r="I18" s="3">
-        <v>454400</v>
+        <v>474900</v>
       </c>
       <c r="J18" s="3">
-        <v>338900</v>
+        <v>374100</v>
       </c>
       <c r="K18" s="3">
         <v>19200</v>
@@ -1186,25 +1186,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>61500</v>
+        <v>10000</v>
       </c>
       <c r="E20" s="3">
-        <v>52000</v>
+        <v>-1600</v>
       </c>
       <c r="F20" s="3">
-        <v>54200</v>
+        <v>1000</v>
       </c>
       <c r="G20" s="3">
-        <v>62700</v>
+        <v>4700</v>
       </c>
       <c r="H20" s="3">
-        <v>57500</v>
+        <v>3400</v>
       </c>
       <c r="I20" s="3">
-        <v>38500</v>
+        <v>-7100</v>
       </c>
       <c r="J20" s="3">
-        <v>20500</v>
+        <v>-6100</v>
       </c>
       <c r="K20" s="3">
         <v>1100</v>
@@ -1231,25 +1231,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>393900</v>
+        <v>326300</v>
       </c>
       <c r="E21" s="3">
-        <v>313900</v>
+        <v>253800</v>
       </c>
       <c r="F21" s="3">
-        <v>-247800</v>
+        <v>356700</v>
       </c>
       <c r="G21" s="3">
-        <v>471200</v>
+        <v>439200</v>
       </c>
       <c r="H21" s="3">
-        <v>606400</v>
+        <v>558300</v>
       </c>
       <c r="I21" s="3">
-        <v>526800</v>
+        <v>517100</v>
       </c>
       <c r="J21" s="3">
-        <v>371200</v>
+        <v>393100</v>
       </c>
       <c r="K21" s="3">
         <v>21400</v>
@@ -1279,22 +1279,22 @@
         <v>8800</v>
       </c>
       <c r="E22" s="3">
-        <v>11800</v>
+        <v>12100</v>
       </c>
       <c r="F22" s="3">
-        <v>10400</v>
+        <v>11600</v>
       </c>
       <c r="G22" s="3">
-        <v>11100</v>
+        <v>12100</v>
       </c>
       <c r="H22" s="3">
-        <v>11100</v>
+        <v>11300</v>
       </c>
       <c r="I22" s="3">
-        <v>8000</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+        <v>8200</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>3</v>
@@ -1321,25 +1321,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>373900</v>
+        <v>364100</v>
       </c>
       <c r="E23" s="3">
-        <v>286400</v>
+        <v>296100</v>
       </c>
       <c r="F23" s="3">
-        <v>-295400</v>
+        <v>-331100</v>
       </c>
       <c r="G23" s="3">
-        <v>408600</v>
+        <v>437500</v>
       </c>
       <c r="H23" s="3">
-        <v>545300</v>
+        <v>552200</v>
       </c>
       <c r="I23" s="3">
-        <v>484900</v>
+        <v>507200</v>
       </c>
       <c r="J23" s="3">
-        <v>359500</v>
+        <v>398000</v>
       </c>
       <c r="K23" s="3">
         <v>20300</v>
@@ -1369,22 +1369,22 @@
         <v>88800</v>
       </c>
       <c r="E24" s="3">
-        <v>79300</v>
+        <v>81500</v>
       </c>
       <c r="F24" s="3">
-        <v>116000</v>
+        <v>129500</v>
       </c>
       <c r="G24" s="3">
-        <v>106500</v>
+        <v>115700</v>
       </c>
       <c r="H24" s="3">
-        <v>124600</v>
+        <v>126900</v>
       </c>
       <c r="I24" s="3">
-        <v>98600</v>
+        <v>101700</v>
       </c>
       <c r="J24" s="3">
-        <v>62700</v>
+        <v>68400</v>
       </c>
       <c r="K24" s="3">
         <v>700</v>
@@ -1456,25 +1456,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>285100</v>
+        <v>275200</v>
       </c>
       <c r="E26" s="3">
-        <v>207100</v>
+        <v>214600</v>
       </c>
       <c r="F26" s="3">
-        <v>-411300</v>
+        <v>-460600</v>
       </c>
       <c r="G26" s="3">
-        <v>302100</v>
+        <v>321700</v>
       </c>
       <c r="H26" s="3">
-        <v>420700</v>
+        <v>425200</v>
       </c>
       <c r="I26" s="3">
-        <v>386300</v>
+        <v>405400</v>
       </c>
       <c r="J26" s="3">
-        <v>296700</v>
+        <v>329600</v>
       </c>
       <c r="K26" s="3">
         <v>19600</v>
@@ -1501,25 +1501,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>276000</v>
+        <v>276100</v>
       </c>
       <c r="E27" s="3">
-        <v>209300</v>
+        <v>215200</v>
       </c>
       <c r="F27" s="3">
-        <v>-410800</v>
+        <v>-458700</v>
       </c>
       <c r="G27" s="3">
-        <v>296500</v>
+        <v>322200</v>
       </c>
       <c r="H27" s="3">
-        <v>418800</v>
+        <v>426700</v>
       </c>
       <c r="I27" s="3">
-        <v>397000</v>
+        <v>409400</v>
       </c>
       <c r="J27" s="3">
-        <v>302800</v>
+        <v>330100</v>
       </c>
       <c r="K27" s="3">
         <v>19600</v>
@@ -1726,25 +1726,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-61500</v>
+        <v>-10000</v>
       </c>
       <c r="E32" s="3">
-        <v>-52000</v>
+        <v>1600</v>
       </c>
       <c r="F32" s="3">
-        <v>-54200</v>
+        <v>-1000</v>
       </c>
       <c r="G32" s="3">
-        <v>-62700</v>
+        <v>-4700</v>
       </c>
       <c r="H32" s="3">
-        <v>-57500</v>
+        <v>-3400</v>
       </c>
       <c r="I32" s="3">
-        <v>-38500</v>
+        <v>7100</v>
       </c>
       <c r="J32" s="3">
-        <v>-20500</v>
+        <v>6100</v>
       </c>
       <c r="K32" s="3">
         <v>-1100</v>
@@ -1771,25 +1771,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>276000</v>
+        <v>276100</v>
       </c>
       <c r="E33" s="3">
-        <v>209300</v>
+        <v>215200</v>
       </c>
       <c r="F33" s="3">
-        <v>-410800</v>
+        <v>-458700</v>
       </c>
       <c r="G33" s="3">
-        <v>296500</v>
+        <v>322200</v>
       </c>
       <c r="H33" s="3">
-        <v>418800</v>
+        <v>426700</v>
       </c>
       <c r="I33" s="3">
-        <v>397000</v>
+        <v>409400</v>
       </c>
       <c r="J33" s="3">
-        <v>302800</v>
+        <v>330100</v>
       </c>
       <c r="K33" s="3">
         <v>19600</v>
@@ -1861,25 +1861,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>276000</v>
+        <v>276100</v>
       </c>
       <c r="E35" s="3">
-        <v>209300</v>
+        <v>215200</v>
       </c>
       <c r="F35" s="3">
-        <v>-410800</v>
+        <v>-458700</v>
       </c>
       <c r="G35" s="3">
-        <v>296500</v>
+        <v>322200</v>
       </c>
       <c r="H35" s="3">
-        <v>418800</v>
+        <v>426700</v>
       </c>
       <c r="I35" s="3">
-        <v>397000</v>
+        <v>409400</v>
       </c>
       <c r="J35" s="3">
-        <v>302800</v>
+        <v>330100</v>
       </c>
       <c r="K35" s="3">
         <v>19600</v>
@@ -1994,25 +1994,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>792400</v>
+        <v>792600</v>
       </c>
       <c r="E41" s="3">
-        <v>707500</v>
+        <v>727600</v>
       </c>
       <c r="F41" s="3">
-        <v>785300</v>
+        <v>876900</v>
       </c>
       <c r="G41" s="3">
-        <v>474200</v>
+        <v>515300</v>
       </c>
       <c r="H41" s="3">
-        <v>368300</v>
+        <v>375200</v>
       </c>
       <c r="I41" s="3">
-        <v>347900</v>
+        <v>358800</v>
       </c>
       <c r="J41" s="3">
-        <v>629100</v>
+        <v>685800</v>
       </c>
       <c r="K41" s="3">
         <v>35600</v>
@@ -2039,25 +2039,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>179100</v>
+        <v>179200</v>
       </c>
       <c r="E42" s="3">
-        <v>789500</v>
+        <v>812000</v>
       </c>
       <c r="F42" s="3">
-        <v>403200</v>
+        <v>450200</v>
       </c>
       <c r="G42" s="3">
-        <v>1066700</v>
+        <v>1158900</v>
       </c>
       <c r="H42" s="3">
-        <v>1735800</v>
+        <v>1768300</v>
       </c>
       <c r="I42" s="3">
-        <v>1244100</v>
+        <v>1283100</v>
       </c>
       <c r="J42" s="3">
-        <v>344300</v>
+        <v>375400</v>
       </c>
       <c r="K42" s="3">
         <v>54400</v>
@@ -2084,25 +2084,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>110100</v>
+        <v>61300</v>
       </c>
       <c r="E43" s="3">
-        <v>118000</v>
+        <v>77700</v>
       </c>
       <c r="F43" s="3">
-        <v>113100</v>
+        <v>75800</v>
       </c>
       <c r="G43" s="3">
-        <v>84600</v>
+        <v>49000</v>
       </c>
       <c r="H43" s="3">
-        <v>73700</v>
+        <v>59600</v>
       </c>
       <c r="I43" s="3">
-        <v>123500</v>
+        <v>117300</v>
       </c>
       <c r="J43" s="3">
-        <v>57800</v>
+        <v>53200</v>
       </c>
       <c r="K43" s="3">
         <v>6100</v>
@@ -2128,26 +2128,26 @@
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2174,25 +2174,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>22700</v>
+        <v>67700</v>
       </c>
       <c r="E45" s="3">
-        <v>38000</v>
+        <v>64700</v>
       </c>
       <c r="F45" s="3">
-        <v>25100</v>
+        <v>71800</v>
       </c>
       <c r="G45" s="3">
-        <v>30500</v>
+        <v>73300</v>
       </c>
       <c r="H45" s="3">
-        <v>48700</v>
+        <v>65100</v>
       </c>
       <c r="I45" s="3">
-        <v>65500</v>
+        <v>77600</v>
       </c>
       <c r="J45" s="3">
-        <v>64700</v>
+        <v>74300</v>
       </c>
       <c r="K45" s="3">
         <v>3400</v>
@@ -2219,25 +2219,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>1104300</v>
+        <v>1104700</v>
       </c>
       <c r="E46" s="3">
-        <v>1652900</v>
+        <v>1699900</v>
       </c>
       <c r="F46" s="3">
-        <v>1326700</v>
+        <v>1481400</v>
       </c>
       <c r="G46" s="3">
-        <v>1656100</v>
+        <v>1799300</v>
       </c>
       <c r="H46" s="3">
-        <v>2226600</v>
+        <v>2268300</v>
       </c>
       <c r="I46" s="3">
-        <v>1781000</v>
+        <v>1836800</v>
       </c>
       <c r="J46" s="3">
-        <v>1090300</v>
+        <v>1188600</v>
       </c>
       <c r="K46" s="3">
         <v>99400</v>
@@ -2264,25 +2264,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>113800</v>
+        <v>664500</v>
       </c>
       <c r="E47" s="3">
-        <v>126000</v>
+        <v>506600</v>
       </c>
       <c r="F47" s="3">
-        <v>115600</v>
+        <v>1262500</v>
       </c>
       <c r="G47" s="3">
-        <v>64100</v>
+        <v>919800</v>
       </c>
       <c r="H47" s="3">
-        <v>69900</v>
+        <v>114300</v>
       </c>
       <c r="I47" s="3">
-        <v>63100</v>
+        <v>65100</v>
       </c>
       <c r="J47" s="3">
-        <v>40700</v>
+        <v>44300</v>
       </c>
       <c r="K47" s="3">
         <v>4400</v>
@@ -2312,22 +2312,22 @@
         <v>108400</v>
       </c>
       <c r="E48" s="3">
-        <v>40700</v>
+        <v>41800</v>
       </c>
       <c r="F48" s="3">
-        <v>61800</v>
+        <v>69000</v>
       </c>
       <c r="G48" s="3">
-        <v>76700</v>
+        <v>83300</v>
       </c>
       <c r="H48" s="3">
-        <v>75700</v>
+        <v>77100</v>
       </c>
       <c r="I48" s="3">
-        <v>54600</v>
+        <v>56300</v>
       </c>
       <c r="J48" s="3">
-        <v>36500</v>
+        <v>39800</v>
       </c>
       <c r="K48" s="3">
         <v>1900</v>
@@ -2357,22 +2357,22 @@
         <v>2400</v>
       </c>
       <c r="E49" s="3">
-        <v>3100</v>
+        <v>3200</v>
       </c>
       <c r="F49" s="3">
-        <v>3900</v>
+        <v>4300</v>
       </c>
       <c r="G49" s="3">
-        <v>673300</v>
+        <v>731500</v>
       </c>
       <c r="H49" s="3">
-        <v>740300</v>
+        <v>754100</v>
       </c>
       <c r="I49" s="3">
-        <v>753400</v>
+        <v>777000</v>
       </c>
       <c r="J49" s="3">
-        <v>10000</v>
+        <v>10900</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>3</v>
@@ -2489,25 +2489,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>959000</v>
+        <v>404100</v>
       </c>
       <c r="E52" s="3">
-        <v>408900</v>
+        <v>38600</v>
       </c>
       <c r="F52" s="3">
-        <v>1045300</v>
+        <v>28300</v>
       </c>
       <c r="G52" s="3">
-        <v>803500</v>
+        <v>17900</v>
       </c>
       <c r="H52" s="3">
-        <v>57300</v>
+        <v>9900</v>
       </c>
       <c r="I52" s="3">
-        <v>21600</v>
+        <v>13900</v>
       </c>
       <c r="J52" s="3">
-        <v>16800</v>
+        <v>11100</v>
       </c>
       <c r="K52" s="3">
         <v>500</v>
@@ -2579,25 +2579,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>2287800</v>
+        <v>2288600</v>
       </c>
       <c r="E54" s="3">
-        <v>2231700</v>
+        <v>2295100</v>
       </c>
       <c r="F54" s="3">
-        <v>2553300</v>
+        <v>2851000</v>
       </c>
       <c r="G54" s="3">
-        <v>3273600</v>
+        <v>3556700</v>
       </c>
       <c r="H54" s="3">
-        <v>3169700</v>
+        <v>3229100</v>
       </c>
       <c r="I54" s="3">
-        <v>2673800</v>
+        <v>2757500</v>
       </c>
       <c r="J54" s="3">
-        <v>1194300</v>
+        <v>1301900</v>
       </c>
       <c r="K54" s="3">
         <v>106300</v>
@@ -2662,25 +2662,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>86900</v>
+        <v>87600</v>
       </c>
       <c r="E57" s="3">
-        <v>87000</v>
+        <v>90800</v>
       </c>
       <c r="F57" s="3">
-        <v>102400</v>
+        <v>115100</v>
       </c>
       <c r="G57" s="3">
-        <v>98600</v>
+        <v>110100</v>
       </c>
       <c r="H57" s="3">
-        <v>100700</v>
+        <v>106800</v>
       </c>
       <c r="I57" s="3">
-        <v>101300</v>
+        <v>110700</v>
       </c>
       <c r="J57" s="3">
-        <v>68400</v>
+        <v>74500</v>
       </c>
       <c r="K57" s="3">
         <v>5600</v>
@@ -2707,25 +2707,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>30400</v>
+        <v>38900</v>
       </c>
       <c r="E58" s="3">
-        <v>373100</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>3</v>
+        <v>396500</v>
+      </c>
+      <c r="F58" s="3">
+        <v>25700</v>
+      </c>
+      <c r="G58" s="3">
+        <v>20300</v>
+      </c>
+      <c r="H58" s="3">
+        <v>19400</v>
+      </c>
+      <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
+        <v>0</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>3</v>
@@ -2752,25 +2752,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>177600</v>
+        <v>107800</v>
       </c>
       <c r="E59" s="3">
-        <v>208000</v>
+        <v>132100</v>
       </c>
       <c r="F59" s="3">
-        <v>252300</v>
+        <v>155800</v>
       </c>
       <c r="G59" s="3">
-        <v>256200</v>
+        <v>155100</v>
       </c>
       <c r="H59" s="3">
-        <v>266800</v>
+        <v>134000</v>
       </c>
       <c r="I59" s="3">
-        <v>278800</v>
+        <v>178900</v>
       </c>
       <c r="J59" s="3">
-        <v>170200</v>
+        <v>117700</v>
       </c>
       <c r="K59" s="3">
         <v>12900</v>
@@ -2797,25 +2797,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>294900</v>
+        <v>295000</v>
       </c>
       <c r="E60" s="3">
-        <v>668000</v>
+        <v>687000</v>
       </c>
       <c r="F60" s="3">
-        <v>354700</v>
+        <v>396000</v>
       </c>
       <c r="G60" s="3">
-        <v>354800</v>
+        <v>385500</v>
       </c>
       <c r="H60" s="3">
-        <v>367500</v>
+        <v>374400</v>
       </c>
       <c r="I60" s="3">
-        <v>380100</v>
+        <v>392000</v>
       </c>
       <c r="J60" s="3">
-        <v>238500</v>
+        <v>260000</v>
       </c>
       <c r="K60" s="3">
         <v>18500</v>
@@ -2842,22 +2842,22 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>276000</v>
+        <v>283500</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>4800</v>
       </c>
       <c r="F61" s="3">
-        <v>643600</v>
+        <v>734900</v>
       </c>
       <c r="G61" s="3">
-        <v>656800</v>
+        <v>734500</v>
       </c>
       <c r="H61" s="3">
-        <v>698500</v>
+        <v>719600</v>
       </c>
       <c r="I61" s="3">
-        <v>687600</v>
+        <v>709100</v>
       </c>
       <c r="J61" s="3">
         <v>0</v>
@@ -2887,25 +2887,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>27000</v>
+        <v>16100</v>
       </c>
       <c r="E62" s="3">
-        <v>22700</v>
+        <v>15300</v>
       </c>
       <c r="F62" s="3">
-        <v>62700</v>
+        <v>20200</v>
       </c>
       <c r="G62" s="3">
-        <v>170500</v>
+        <v>138100</v>
       </c>
       <c r="H62" s="3">
-        <v>169700</v>
+        <v>132800</v>
       </c>
       <c r="I62" s="3">
-        <v>52100</v>
+        <v>16000</v>
       </c>
       <c r="J62" s="3">
-        <v>3800</v>
+        <v>2300</v>
       </c>
       <c r="K62" s="3">
         <v>300</v>
@@ -3067,25 +3067,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>623600</v>
+        <v>598100</v>
       </c>
       <c r="E66" s="3">
-        <v>712300</v>
+        <v>710300</v>
       </c>
       <c r="F66" s="3">
-        <v>1080600</v>
+        <v>1184700</v>
       </c>
       <c r="G66" s="3">
-        <v>1209800</v>
+        <v>1284400</v>
       </c>
       <c r="H66" s="3">
-        <v>1262300</v>
+        <v>1258800</v>
       </c>
       <c r="I66" s="3">
-        <v>1132800</v>
+        <v>1154800</v>
       </c>
       <c r="J66" s="3">
-        <v>245000</v>
+        <v>264200</v>
       </c>
       <c r="K66" s="3">
         <v>18700</v>
@@ -3311,25 +3311,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>891100</v>
+        <v>891300</v>
       </c>
       <c r="E72" s="3">
-        <v>750100</v>
+        <v>771500</v>
       </c>
       <c r="F72" s="3">
-        <v>659500</v>
+        <v>736300</v>
       </c>
       <c r="G72" s="3">
-        <v>1190400</v>
+        <v>1293400</v>
       </c>
       <c r="H72" s="3">
-        <v>1052400</v>
+        <v>1072100</v>
       </c>
       <c r="I72" s="3">
-        <v>755800</v>
+        <v>779500</v>
       </c>
       <c r="J72" s="3">
-        <v>358800</v>
+        <v>391200</v>
       </c>
       <c r="K72" s="3">
         <v>7100</v>
@@ -3491,25 +3491,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>1664300</v>
+        <v>1664800</v>
       </c>
       <c r="E76" s="3">
-        <v>1519400</v>
+        <v>1562600</v>
       </c>
       <c r="F76" s="3">
-        <v>1472800</v>
+        <v>1644500</v>
       </c>
       <c r="G76" s="3">
-        <v>2063800</v>
+        <v>2242300</v>
       </c>
       <c r="H76" s="3">
-        <v>1907500</v>
+        <v>1943200</v>
       </c>
       <c r="I76" s="3">
-        <v>1541000</v>
+        <v>1589300</v>
       </c>
       <c r="J76" s="3">
-        <v>949300</v>
+        <v>1034900</v>
       </c>
       <c r="K76" s="3">
         <v>87500</v>
@@ -3631,25 +3631,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>276000</v>
+        <v>276100</v>
       </c>
       <c r="E81" s="3">
-        <v>209300</v>
+        <v>215200</v>
       </c>
       <c r="F81" s="3">
-        <v>-410800</v>
+        <v>-458700</v>
       </c>
       <c r="G81" s="3">
-        <v>296500</v>
+        <v>322200</v>
       </c>
       <c r="H81" s="3">
-        <v>418800</v>
+        <v>426700</v>
       </c>
       <c r="I81" s="3">
-        <v>397000</v>
+        <v>409400</v>
       </c>
       <c r="J81" s="3">
-        <v>302800</v>
+        <v>330100</v>
       </c>
       <c r="K81" s="3">
         <v>19600</v>
@@ -3695,25 +3695,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>11200</v>
+        <v>10500</v>
       </c>
       <c r="E83" s="3">
-        <v>15800</v>
+        <v>15500</v>
       </c>
       <c r="F83" s="3">
-        <v>37300</v>
+        <v>24500</v>
       </c>
       <c r="G83" s="3">
-        <v>51600</v>
+        <v>32000</v>
       </c>
       <c r="H83" s="3">
-        <v>50200</v>
+        <v>28500</v>
       </c>
       <c r="I83" s="3">
-        <v>34000</v>
+        <v>21600</v>
       </c>
       <c r="J83" s="3">
-        <v>11800</v>
+        <v>12100</v>
       </c>
       <c r="K83" s="3">
         <v>1200</v>
@@ -3965,25 +3965,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>321000</v>
+        <v>321100</v>
       </c>
       <c r="E89" s="3">
-        <v>173000</v>
+        <v>177900</v>
       </c>
       <c r="F89" s="3">
-        <v>219800</v>
+        <v>245400</v>
       </c>
       <c r="G89" s="3">
-        <v>434300</v>
+        <v>471900</v>
       </c>
       <c r="H89" s="3">
-        <v>768200</v>
+        <v>782600</v>
       </c>
       <c r="I89" s="3">
-        <v>469100</v>
+        <v>483800</v>
       </c>
       <c r="J89" s="3">
-        <v>406900</v>
+        <v>443600</v>
       </c>
       <c r="K89" s="3">
         <v>30100</v>
@@ -4029,25 +4029,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-81200</v>
+        <v>-81300</v>
       </c>
       <c r="E91" s="3">
-        <v>-11300</v>
+        <v>-11700</v>
       </c>
       <c r="F91" s="3">
-        <v>-13400</v>
+        <v>-15000</v>
       </c>
       <c r="G91" s="3">
-        <v>-17500</v>
+        <v>-19000</v>
       </c>
       <c r="H91" s="3">
-        <v>-26300</v>
+        <v>-26800</v>
       </c>
       <c r="I91" s="3">
-        <v>-34200</v>
+        <v>-35300</v>
       </c>
       <c r="J91" s="3">
-        <v>-30800</v>
+        <v>-33600</v>
       </c>
       <c r="K91" s="3">
         <v>-1000</v>
@@ -4164,25 +4164,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>340200</v>
+        <v>340300</v>
       </c>
       <c r="E94" s="3">
-        <v>241900</v>
+        <v>248800</v>
       </c>
       <c r="F94" s="3">
-        <v>359500</v>
+        <v>401500</v>
       </c>
       <c r="G94" s="3">
-        <v>-105500</v>
+        <v>-114600</v>
       </c>
       <c r="H94" s="3">
-        <v>-568100</v>
+        <v>-578800</v>
       </c>
       <c r="I94" s="3">
-        <v>-1414600</v>
+        <v>-1458900</v>
       </c>
       <c r="J94" s="3">
-        <v>-26500</v>
+        <v>-28900</v>
       </c>
       <c r="K94" s="3">
         <v>-16300</v>
@@ -4228,19 +4228,19 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-135100</v>
+        <v>135100</v>
       </c>
       <c r="E96" s="3">
-        <v>-118600</v>
+        <v>121900</v>
       </c>
       <c r="F96" s="3">
-        <v>-120200</v>
+        <v>134200</v>
       </c>
       <c r="G96" s="3">
-        <v>-158500</v>
+        <v>172200</v>
       </c>
       <c r="H96" s="3">
-        <v>-123700</v>
+        <v>1400</v>
       </c>
       <c r="I96" s="3">
         <v>0</v>
@@ -4411,19 +4411,19 @@
         <v>-239700</v>
       </c>
       <c r="E100" s="3">
-        <v>-483900</v>
+        <v>-497700</v>
       </c>
       <c r="F100" s="3">
-        <v>-251900</v>
+        <v>-281300</v>
       </c>
       <c r="G100" s="3">
-        <v>-211200</v>
+        <v>-229500</v>
       </c>
       <c r="H100" s="3">
-        <v>-179600</v>
+        <v>-182900</v>
       </c>
       <c r="I100" s="3">
-        <v>660900</v>
+        <v>681600</v>
       </c>
       <c r="J100" s="3">
         <v>400</v>
@@ -4456,22 +4456,22 @@
         <v>13300</v>
       </c>
       <c r="E101" s="3">
-        <v>5800</v>
+        <v>6000</v>
       </c>
       <c r="F101" s="3">
-        <v>-5900</v>
+        <v>-6600</v>
       </c>
       <c r="G101" s="3">
-        <v>-11400</v>
+        <v>-12400</v>
       </c>
       <c r="H101" s="3">
         <v>-100</v>
       </c>
       <c r="I101" s="3">
-        <v>3400</v>
+        <v>3500</v>
       </c>
       <c r="J101" s="3">
-        <v>-3800</v>
+        <v>-4100</v>
       </c>
       <c r="K101" s="3">
         <v>-1600</v>
@@ -4498,25 +4498,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>434800</v>
+        <v>435000</v>
       </c>
       <c r="E102" s="3">
-        <v>-63200</v>
+        <v>-65000</v>
       </c>
       <c r="F102" s="3">
-        <v>321600</v>
+        <v>359100</v>
       </c>
       <c r="G102" s="3">
-        <v>106200</v>
+        <v>115400</v>
       </c>
       <c r="H102" s="3">
-        <v>20400</v>
+        <v>20800</v>
       </c>
       <c r="I102" s="3">
-        <v>-281100</v>
+        <v>-289900</v>
       </c>
       <c r="J102" s="3">
-        <v>377000</v>
+        <v>410900</v>
       </c>
       <c r="K102" s="3">
         <v>12200</v>

--- a/AAII_Financials/Yearly/MOMO_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/MOMO_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="92">
   <si>
     <t>MOMO</t>
   </si>
@@ -656,208 +656,220 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42735</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42369</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42004</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41639</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41274</v>
       </c>
-      <c r="P7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>1447200</v>
+      </c>
+      <c r="E8" s="3">
         <v>1692600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1841900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2294400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2301300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2443700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1949600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1365700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>76400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>19200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>7100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>500</v>
       </c>
-      <c r="O8" s="3">
-        <v>0</v>
-      </c>
-      <c r="P8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="P8" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>883300</v>
+      </c>
+      <c r="E9" s="3">
         <v>990800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1076000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1319700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1221800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1219600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1044400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>672100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>33300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>4400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>400</v>
       </c>
-      <c r="O9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>563900</v>
+      </c>
+      <c r="E10" s="3">
         <v>701900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>765900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>974800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1079500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1224100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>905200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>693600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>43000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>14900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>4600</v>
       </c>
-      <c r="N10" s="3">
-        <v>0</v>
-      </c>
-      <c r="O10" s="3" t="s">
-        <v>3</v>
+      <c r="O10" s="3">
+        <v>0</v>
       </c>
       <c r="P10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -875,53 +887,57 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>110200</v>
+      </c>
+      <c r="E12" s="3">
         <v>124800</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>145900</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>178200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>178900</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>157300</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>110600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>53200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>4300</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>3300</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>1500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>500</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>200</v>
       </c>
-      <c r="P12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -964,39 +980,42 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3">
         <v>3800</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-17200</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>695000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>1600</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>2300</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>6300</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>4600</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>800</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1009,36 +1028,39 @@
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E15" s="3">
         <v>11200</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>16300</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>41700</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>56100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>51200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>35100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>12900</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1054,9 +1076,12 @@
       <c r="P15" s="3">
         <v>0</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1071,98 +1096,105 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1237200</v>
+      </c>
+      <c r="E17" s="3">
         <v>1367600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1606000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1978400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1913500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1933200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1474600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>991600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>57200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>18400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>11200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>600</v>
       </c>
-      <c r="P17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>210000</v>
+      </c>
+      <c r="E18" s="3">
         <v>325100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>236000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>316000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>387700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>510500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>474900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>374100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>19200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-4100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-1400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-600</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1180,122 +1212,129 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E20" s="3">
         <v>10000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-1600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>1000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>4700</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>3400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-7100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-6100</v>
-      </c>
-      <c r="K20" s="3">
-        <v>1100</v>
       </c>
       <c r="L20" s="3">
         <v>1100</v>
       </c>
       <c r="M20" s="3">
+        <v>1100</v>
+      </c>
+      <c r="N20" s="3">
         <v>100</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
         <v>0</v>
       </c>
-      <c r="P20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>213800</v>
+      </c>
+      <c r="E21" s="3">
         <v>326300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>253800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>356700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>439200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>558300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>517100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>393100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>21400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>2900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-3600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-1300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-500</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>17500</v>
+      </c>
+      <c r="E22" s="3">
         <v>8800</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>12100</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>11600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>12100</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>11300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>8200</v>
       </c>
-      <c r="J22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1311,87 +1350,93 @@
       <c r="O22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="P22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>258200</v>
+      </c>
+      <c r="E23" s="3">
         <v>364100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>296100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-331100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>437500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>552200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>507200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>398000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>20300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-4000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-1400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-600</v>
       </c>
-      <c r="P23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>115800</v>
+      </c>
+      <c r="E24" s="3">
         <v>88800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>81500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>129500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>115700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>126900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>101700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>68400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>700</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
-      </c>
       <c r="M24" s="3">
         <v>0</v>
       </c>
@@ -1401,12 +1446,15 @@
       <c r="O24" s="3">
         <v>0</v>
       </c>
-      <c r="P24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="P24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1449,99 +1497,108 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>142400</v>
+      </c>
+      <c r="E26" s="3">
         <v>275200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>214600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-460600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>321700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>425200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>405400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>329600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>19600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-4000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-1400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-600</v>
       </c>
-      <c r="P26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>142400</v>
+      </c>
+      <c r="E27" s="3">
         <v>276100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>215200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-458700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>322200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>426700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>409400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>330100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>19600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-13100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-2700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-1000</v>
       </c>
-      <c r="P27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1584,9 +1641,12 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1629,9 +1689,12 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1674,9 +1737,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1719,99 +1785,108 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="E32" s="3">
         <v>-10000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>1600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-1000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-4700</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-3400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>7100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>6100</v>
-      </c>
-      <c r="K32" s="3">
-        <v>-1100</v>
       </c>
       <c r="L32" s="3">
         <v>-1100</v>
       </c>
       <c r="M32" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="N32" s="3">
         <v>-100</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
         <v>0</v>
       </c>
-      <c r="P32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>142400</v>
+      </c>
+      <c r="E33" s="3">
         <v>276100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>215200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-458700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>322200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>426700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>409400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>330100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>19600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-13100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-2700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-1000</v>
       </c>
-      <c r="P33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1854,104 +1929,113 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>142400</v>
+      </c>
+      <c r="E35" s="3">
         <v>276100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>215200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-458700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>322200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>426700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>409400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>330100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>19600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-13100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-2700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-1000</v>
       </c>
-      <c r="P35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42735</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42369</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42004</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41639</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41274</v>
       </c>
-      <c r="P38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1969,8 +2053,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1988,86 +2073,90 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>564800</v>
+      </c>
+      <c r="E41" s="3">
         <v>792600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>727600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>876900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>515300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>375200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>358800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>685800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>35600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>24300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>71100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>8400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2700</v>
       </c>
-      <c r="P41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>277600</v>
+      </c>
+      <c r="E42" s="3">
         <v>179200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>812000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>450200</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>1158900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>1768300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>1283100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>375400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>54400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>43100</v>
       </c>
-      <c r="M42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2077,54 +2166,60 @@
       <c r="P42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>26300</v>
+      </c>
+      <c r="E43" s="3">
         <v>61300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>77700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>75800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>49000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>59600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>117300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>53200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>6100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>100</v>
       </c>
-      <c r="P43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2149,8 +2244,8 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -2167,216 +2262,231 @@
       <c r="P44" s="3">
         <v>0</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E45" s="3">
         <v>67700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>64700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>71800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>73300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>65100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>77600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>74300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>3400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>100</v>
       </c>
-      <c r="O45" s="3">
-        <v>0</v>
-      </c>
-      <c r="P45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="P45" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1645700</v>
+      </c>
+      <c r="E46" s="3">
         <v>1104700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1699900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1481400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1799300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2268300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1836800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1188600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>99400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>72400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>73500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>8900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2800</v>
       </c>
-      <c r="P46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>532300</v>
+      </c>
+      <c r="E47" s="3">
         <v>664500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>506600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1262500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>919800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>114300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>65100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>44300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>4400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>2800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>100</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
-      </c>
-      <c r="P47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="P47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>157400</v>
+      </c>
+      <c r="E48" s="3">
         <v>108400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>41800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>69000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>83300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>77100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>56300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>39800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>100</v>
       </c>
-      <c r="P48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>30500</v>
+      </c>
+      <c r="E49" s="3">
         <v>2400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>3200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>4300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>731500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>754100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>777000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>10900</v>
       </c>
-      <c r="K49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2392,9 +2502,12 @@
       <c r="P49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2437,9 +2550,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2482,54 +2598,60 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>147600</v>
+      </c>
+      <c r="E52" s="3">
         <v>404100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>38600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>28300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>17900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>9900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>13900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>11100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>100</v>
       </c>
-      <c r="N52" s="3">
-        <v>0</v>
-      </c>
-      <c r="O52" s="3" t="s">
-        <v>3</v>
+      <c r="O52" s="3">
+        <v>0</v>
       </c>
       <c r="P52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2572,54 +2694,60 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2518500</v>
+      </c>
+      <c r="E54" s="3">
         <v>2288600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2295100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2851000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>3556700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>3229100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2757500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1301900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>106300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>77900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>75500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>9600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>3000</v>
       </c>
-      <c r="P54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2637,8 +2765,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2656,82 +2785,86 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>84300</v>
+      </c>
+      <c r="E57" s="3">
         <v>87600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>90800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>115100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>110100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>106800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>110700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>74500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>5600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>100</v>
       </c>
-      <c r="O57" s="3">
-        <v>0</v>
-      </c>
-      <c r="P57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="P57" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>611900</v>
+      </c>
+      <c r="E58" s="3">
         <v>38900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>396500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>25700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>20300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>19400</v>
       </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
       <c r="J58" s="3">
         <v>0</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L58" s="3">
-        <v>0</v>
+      <c r="K58" s="3">
+        <v>0</v>
+      </c>
+      <c r="L58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M58" s="3">
         <v>0</v>
@@ -2745,123 +2878,132 @@
       <c r="P58" s="3">
         <v>0</v>
       </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>84000</v>
+      </c>
+      <c r="E59" s="3">
         <v>107800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>132100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>155800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>155100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>134000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>178900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>117700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>12900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>8800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>5100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>800</v>
       </c>
-      <c r="O59" s="3">
-        <v>0</v>
-      </c>
-      <c r="P59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="P59" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>876600</v>
+      </c>
+      <c r="E60" s="3">
         <v>295000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>687000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>396000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>385500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>374400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>392000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>260000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>18500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>10300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>6000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>800</v>
       </c>
-      <c r="O60" s="3">
-        <v>0</v>
-      </c>
-      <c r="P60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="P60" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>15800</v>
+      </c>
+      <c r="E61" s="3">
         <v>283500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>4800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>734900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>734500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>719600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>709100</v>
       </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
       <c r="K61" s="3">
         <v>0</v>
       </c>
@@ -2880,41 +3022,44 @@
       <c r="P61" s="3">
         <v>0</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>26700</v>
+      </c>
+      <c r="E62" s="3">
         <v>16100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>15300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>20200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>138100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>132800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>16000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2300</v>
-      </c>
-      <c r="K62" s="3">
-        <v>300</v>
       </c>
       <c r="L62" s="3">
         <v>300</v>
       </c>
-      <c r="M62" s="3" t="s">
-        <v>3</v>
+      <c r="M62" s="3">
+        <v>300</v>
       </c>
       <c r="N62" s="3" t="s">
         <v>3</v>
@@ -2925,9 +3070,12 @@
       <c r="P62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2970,9 +3118,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3015,9 +3166,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3060,54 +3214,60 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>952200</v>
+      </c>
+      <c r="E66" s="3">
         <v>598100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>710300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1184700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1284400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1258800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1154800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>264200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>18700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>10600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>6000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>800</v>
       </c>
-      <c r="O66" s="3">
-        <v>0</v>
-      </c>
-      <c r="P66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="P66" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3125,8 +3285,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3169,9 +3330,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3214,9 +3378,12 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3251,17 +3418,20 @@
         <v>0</v>
       </c>
       <c r="N70" s="3">
+        <v>0</v>
+      </c>
+      <c r="O70" s="3">
         <v>12200</v>
       </c>
-      <c r="O70" s="3">
+      <c r="P70" s="3">
         <v>3900</v>
       </c>
-      <c r="P70" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3304,54 +3474,60 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3">
+      <c r="D72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E72" s="3">
         <v>891300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>771500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>736300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1293400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1072100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>779500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>391200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>7100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-13500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-17000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-3800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-1000</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3394,9 +3570,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3439,9 +3618,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3484,54 +3666,60 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1566300</v>
+      </c>
+      <c r="E76" s="3">
         <v>1664800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1562600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1644500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2242300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1943200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1589300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1034900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>87500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>67300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>69500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-3500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-900</v>
       </c>
-      <c r="P76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3574,104 +3762,113 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42735</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42369</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42004</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41639</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41274</v>
       </c>
-      <c r="P80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>142400</v>
+      </c>
+      <c r="E81" s="3">
         <v>276100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>215200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-458700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>322200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>426700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>409400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>330100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>19600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-13100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-2700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-1000</v>
       </c>
-      <c r="P81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3689,53 +3886,57 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>7200</v>
+      </c>
+      <c r="E83" s="3">
         <v>10500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>15500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>24500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>32000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>28500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>21600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>12100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>100</v>
       </c>
-      <c r="O83" s="3">
-        <v>0</v>
-      </c>
-      <c r="P83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="P83" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3778,9 +3979,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3823,9 +4027,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3868,9 +4075,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3913,9 +4123,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3958,54 +4171,60 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>224700</v>
+      </c>
+      <c r="E89" s="3">
         <v>321100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>177900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>245400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>471900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>782600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>483800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>443600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>30100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>8200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-600</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4023,53 +4242,57 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-39100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-81300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-11700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-15000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-19000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-26800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-35300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-33600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-100</v>
       </c>
-      <c r="P91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4112,9 +4335,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4157,54 +4383,60 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-76600</v>
+      </c>
+      <c r="E94" s="3">
         <v>340300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>248800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>401500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-114600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-578800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1458900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-28900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-16300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-47900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-300</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4222,29 +4454,30 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>98100</v>
+      </c>
+      <c r="E96" s="3">
         <v>135100</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>121900</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>134200</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>172200</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>1400</v>
       </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
       <c r="J96" s="3">
         <v>0</v>
       </c>
@@ -4266,9 +4499,12 @@
       <c r="P96" s="3">
         <v>0</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4311,9 +4547,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4356,9 +4595,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4401,142 +4643,154 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>32400</v>
+      </c>
+      <c r="E100" s="3">
         <v>-239700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-497700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-281300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-229500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-182900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>681600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>400</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
       <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>-300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>65000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>6800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>3400</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E101" s="3">
         <v>13300</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>6000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-6600</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-12400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>3500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-4100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-1600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-200</v>
       </c>
-      <c r="N101" s="3">
-        <v>0</v>
-      </c>
       <c r="O101" s="3">
         <v>0</v>
       </c>
-      <c r="P101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>186300</v>
+      </c>
+      <c r="E102" s="3">
         <v>435000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-65000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>359100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>115400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>20800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-289900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>410900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>12200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-40400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>62400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>5600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>2500</v>
       </c>
-      <c r="P102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q102" s="3"/>
+      <c r="Q102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/MOMO_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/MOMO_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="92">
   <si>
     <t>MOMO</t>
   </si>
@@ -989,8 +989,8 @@
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
+      <c r="D14" s="3">
+        <v>12400</v>
       </c>
       <c r="E14" s="3">
         <v>3800</v>
@@ -1219,7 +1219,7 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>4300</v>
+        <v>-8100</v>
       </c>
       <c r="E20" s="3">
         <v>10000</v>
@@ -1267,7 +1267,7 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>213800</v>
+        <v>226200</v>
       </c>
       <c r="E21" s="3">
         <v>326300</v>
@@ -1795,7 +1795,7 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-4300</v>
+        <v>8100</v>
       </c>
       <c r="E32" s="3">
         <v>-10000</v>
@@ -2176,10 +2176,10 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>26300</v>
+        <v>109000</v>
       </c>
       <c r="E43" s="3">
-        <v>61300</v>
+        <v>62300</v>
       </c>
       <c r="F43" s="3">
         <v>77700</v>
@@ -2271,11 +2271,11 @@
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>3</v>
+      <c r="D45" s="3">
+        <v>67100</v>
       </c>
       <c r="E45" s="3">
-        <v>67700</v>
+        <v>66700</v>
       </c>
       <c r="F45" s="3">
         <v>64700</v>
@@ -2888,10 +2888,10 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>84000</v>
+        <v>115500</v>
       </c>
       <c r="E59" s="3">
-        <v>107800</v>
+        <v>107500</v>
       </c>
       <c r="F59" s="3">
         <v>132100</v>
@@ -3483,8 +3483,8 @@
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3" t="s">
-        <v>3</v>
+      <c r="D72" s="3">
+        <v>910200</v>
       </c>
       <c r="E72" s="3">
         <v>891300</v>
@@ -3676,7 +3676,7 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>1566300</v>
+        <v>1540700</v>
       </c>
       <c r="E76" s="3">
         <v>1664800</v>

--- a/AAII_Financials/Yearly/MOMO_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/MOMO_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="92">
   <si>
     <t>MOMO</t>
   </si>
@@ -656,220 +656,232 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43100</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42735</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42369</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>42004</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41639</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41274</v>
       </c>
-      <c r="Q7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="R7" s="2"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="S7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>1482200</v>
+      </c>
+      <c r="E8" s="3">
         <v>1447200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1692600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1841900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2294400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2301300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2443700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1949600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1365700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>76400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>19200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>7100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>500</v>
       </c>
-      <c r="P8" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3">
+        <v>0</v>
+      </c>
+      <c r="R8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>921700</v>
+      </c>
+      <c r="E9" s="3">
         <v>883300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>990800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1076000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1319700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1221800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1219600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1044400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>672100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>33300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>4400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>400</v>
       </c>
-      <c r="P9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>560500</v>
+      </c>
+      <c r="E10" s="3">
         <v>563900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>701900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>765900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>974800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1079500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1224100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>905200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>693600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>43000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>14900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>4600</v>
       </c>
-      <c r="O10" s="3">
-        <v>0</v>
-      </c>
-      <c r="P10" s="3" t="s">
-        <v>3</v>
+      <c r="P10" s="3">
+        <v>0</v>
       </c>
       <c r="Q10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -888,56 +900,60 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>111400</v>
+      </c>
+      <c r="E12" s="3">
         <v>110200</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>124800</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>145900</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>178200</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>178900</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>157300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>110600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>53200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>4300</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>3300</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>1500</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>500</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>200</v>
       </c>
-      <c r="Q12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -983,42 +999,45 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-      <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E14" s="3">
         <v>12400</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>3800</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-17200</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>695000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>1600</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>2300</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>6300</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>4600</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>800</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1031,39 +1050,42 @@
       <c r="Q14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>11700</v>
+      </c>
+      <c r="E15" s="3">
         <v>8000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>11200</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>16300</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>41700</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>56100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>51200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>35100</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>12900</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1079,9 +1101,12 @@
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-      <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1097,104 +1122,111 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1288500</v>
+      </c>
+      <c r="E17" s="3">
         <v>1237200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1367600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1606000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1978400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1913500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1933200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1474600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>991600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>57200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>18400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>11200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>600</v>
       </c>
-      <c r="Q17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S17" s="3"/>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>193700</v>
+      </c>
+      <c r="E18" s="3">
         <v>210000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>325100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>236000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>316000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>387700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>510500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>474900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>374100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>19200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-4100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-1400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-600</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1213,131 +1245,138 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E20" s="3">
         <v>-8100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>10000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-1600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>1000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>4700</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>3400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-7100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-6100</v>
-      </c>
-      <c r="L20" s="3">
-        <v>1100</v>
       </c>
       <c r="M20" s="3">
         <v>1100</v>
       </c>
       <c r="N20" s="3">
+        <v>1100</v>
+      </c>
+      <c r="O20" s="3">
         <v>100</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
         <v>0</v>
       </c>
-      <c r="Q20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>203500</v>
+      </c>
+      <c r="E21" s="3">
         <v>226200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>326300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>253800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>356700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>439200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>558300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>517100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>393100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>21400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>2900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-3600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-1300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-500</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>10400</v>
+      </c>
+      <c r="E22" s="3">
         <v>17500</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>8800</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>12100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>11600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>12100</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>11300</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>8200</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1353,93 +1392,99 @@
       <c r="P22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
-      </c>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>235800</v>
+      </c>
+      <c r="E23" s="3">
         <v>258200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>364100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>296100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-331100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>437500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>552200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>507200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>398000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>20300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-4000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-1400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-600</v>
       </c>
-      <c r="Q23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>120500</v>
+      </c>
+      <c r="E24" s="3">
         <v>115800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>88800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>81500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>129500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>115700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>126900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>101700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>68400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>700</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
-      </c>
       <c r="N24" s="3">
         <v>0</v>
       </c>
@@ -1449,12 +1494,15 @@
       <c r="P24" s="3">
         <v>0</v>
       </c>
-      <c r="Q24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R24" s="3"/>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+      <c r="R24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1500,105 +1548,114 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-      <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>115300</v>
+      </c>
+      <c r="E26" s="3">
         <v>142400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>275200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>214600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-460600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>321700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>425200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>405400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>329600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>19600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-4000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-1400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-600</v>
       </c>
-      <c r="Q26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R26" s="3"/>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>115000</v>
+      </c>
+      <c r="E27" s="3">
         <v>142400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>276100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>215200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-458700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>322200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>426700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>409400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>330100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>19600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-13100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-2700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R27" s="3"/>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1644,9 +1701,12 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-      <c r="R28" s="3"/>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1692,9 +1752,12 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-      <c r="R29" s="3"/>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1740,9 +1803,12 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-      <c r="R30" s="3"/>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1788,105 +1854,114 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-      <c r="R31" s="3"/>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E32" s="3">
         <v>8100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-10000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>1600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-1000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-4700</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-3400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>7100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>6100</v>
-      </c>
-      <c r="L32" s="3">
-        <v>-1100</v>
       </c>
       <c r="M32" s="3">
         <v>-1100</v>
       </c>
       <c r="N32" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="O32" s="3">
         <v>-100</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
         <v>0</v>
       </c>
-      <c r="Q32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R32" s="3"/>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>115000</v>
+      </c>
+      <c r="E33" s="3">
         <v>142400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>276100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>215200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-458700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>322200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>426700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>409400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>330100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>19600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-13100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-2700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R33" s="3"/>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S33" s="3"/>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1932,110 +2007,119 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-      <c r="R34" s="3"/>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3"/>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>115000</v>
+      </c>
+      <c r="E35" s="3">
         <v>142400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>276100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>215200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-458700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>322200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>426700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>409400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>330100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>19600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-13100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-2700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R35" s="3"/>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S35" s="3"/>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43100</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42735</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42369</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>42004</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41639</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41274</v>
       </c>
-      <c r="Q38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="R38" s="2"/>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="S38" s="2"/>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2054,8 +2138,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2074,92 +2159,96 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>760600</v>
+      </c>
+      <c r="E41" s="3">
         <v>564800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>792600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>727600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>876900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>515300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>375200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>358800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>685800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>35600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>24300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>71100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>8400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2700</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R41" s="3"/>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>462800</v>
+      </c>
+      <c r="E42" s="3">
         <v>277600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>179200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>812000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>450200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>1158900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>1768300</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>1283100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>375400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>54400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>43100</v>
       </c>
-      <c r="N42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2169,57 +2258,63 @@
       <c r="Q42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R42" s="3"/>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>73600</v>
+      </c>
+      <c r="E43" s="3">
         <v>109000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>62300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>77700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>75800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>49000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>59600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>117300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>53200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>6100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>100</v>
       </c>
-      <c r="Q43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R43" s="3"/>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2247,8 +2342,8 @@
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -2265,231 +2360,246 @@
       <c r="Q44" s="3">
         <v>0</v>
       </c>
-      <c r="R44" s="3"/>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R44" s="3">
+        <v>0</v>
+      </c>
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>69900</v>
+      </c>
+      <c r="E45" s="3">
         <v>67100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>66700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>64700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>71800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>73300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>65100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>77600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>74300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>3400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>100</v>
       </c>
-      <c r="P45" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R45" s="3"/>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3">
+        <v>0</v>
+      </c>
+      <c r="R45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1392100</v>
+      </c>
+      <c r="E46" s="3">
         <v>1645700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1104700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1699900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1481400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1799300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2268300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1836800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1188600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>99400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>72400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>73500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>8900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2800</v>
       </c>
-      <c r="Q46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R46" s="3"/>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S46" s="3"/>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>216500</v>
+      </c>
+      <c r="E47" s="3">
         <v>532300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>664500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>506600</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1262500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>919800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>114300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>65100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>44300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>4400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>2800</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>100</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R47" s="3"/>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+      <c r="R47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S47" s="3"/>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>220000</v>
+      </c>
+      <c r="E48" s="3">
         <v>157400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>108400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>41800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>69000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>83300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>77100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>56300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>39800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>100</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R48" s="3"/>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S48" s="3"/>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>119700</v>
+      </c>
+      <c r="E49" s="3">
         <v>30500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>3200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>4300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>731500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>754100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>777000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>10900</v>
       </c>
-      <c r="L49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2505,9 +2615,12 @@
       <c r="Q49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R49" s="3"/>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S49" s="3"/>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2553,9 +2666,12 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-      <c r="R50" s="3"/>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3"/>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2601,57 +2717,63 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-      <c r="R51" s="3"/>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3"/>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>16900</v>
+      </c>
+      <c r="E52" s="3">
         <v>147600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>404100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>38600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>28300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>17900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>9900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>13900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>11100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>100</v>
       </c>
-      <c r="O52" s="3">
-        <v>0</v>
-      </c>
-      <c r="P52" s="3" t="s">
-        <v>3</v>
+      <c r="P52" s="3">
+        <v>0</v>
       </c>
       <c r="Q52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R52" s="3"/>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S52" s="3"/>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2697,57 +2819,63 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-      <c r="R53" s="3"/>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3"/>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1970000</v>
+      </c>
+      <c r="E54" s="3">
         <v>2518500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2288600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2295100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2851000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>3556700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>3229100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2757500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1301900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>106300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>77900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>75500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>9600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>3000</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R54" s="3"/>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S54" s="3"/>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2766,8 +2894,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2786,88 +2915,92 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>83600</v>
+      </c>
+      <c r="E57" s="3">
         <v>84300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>87600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>90800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>115100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>110100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>106800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>110700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>74500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>5600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>100</v>
       </c>
-      <c r="P57" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R57" s="3"/>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3">
+        <v>0</v>
+      </c>
+      <c r="R57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S57" s="3"/>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>12300</v>
+      </c>
+      <c r="E58" s="3">
         <v>611900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>38900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>396500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>25700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>20300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>19400</v>
       </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
       <c r="K58" s="3">
         <v>0</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M58" s="3">
-        <v>0</v>
+      <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N58" s="3">
         <v>0</v>
@@ -2881,132 +3014,141 @@
       <c r="Q58" s="3">
         <v>0</v>
       </c>
-      <c r="R58" s="3"/>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R58" s="3">
+        <v>0</v>
+      </c>
+      <c r="S58" s="3"/>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>135000</v>
+      </c>
+      <c r="E59" s="3">
         <v>115500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>107500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>132100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>155800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>155100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>134000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>178900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>117700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>12900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>8800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>5100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>800</v>
       </c>
-      <c r="P59" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R59" s="3"/>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3">
+        <v>0</v>
+      </c>
+      <c r="R59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>297400</v>
+      </c>
+      <c r="E60" s="3">
         <v>876600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>295000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>687000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>396000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>385500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>374400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>392000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>260000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>18500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>10300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>6000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>800</v>
       </c>
-      <c r="P60" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R60" s="3"/>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3">
+        <v>0</v>
+      </c>
+      <c r="R60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S60" s="3"/>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E61" s="3">
         <v>15800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>283500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>4800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>734900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>734500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>719600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>709100</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
@@ -3025,44 +3167,47 @@
       <c r="Q61" s="3">
         <v>0</v>
       </c>
-      <c r="R61" s="3"/>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+      <c r="S61" s="3"/>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E62" s="3">
         <v>26700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>16100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>15300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>20200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>138100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>132800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>16000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2300</v>
-      </c>
-      <c r="L62" s="3">
-        <v>300</v>
       </c>
       <c r="M62" s="3">
         <v>300</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>3</v>
+      <c r="N62" s="3">
+        <v>300</v>
       </c>
       <c r="O62" s="3" t="s">
         <v>3</v>
@@ -3073,9 +3218,12 @@
       <c r="Q62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R62" s="3"/>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S62" s="3"/>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3121,9 +3269,12 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-      <c r="R63" s="3"/>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3"/>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3169,9 +3320,12 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-      <c r="R64" s="3"/>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3"/>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3217,57 +3371,63 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-      <c r="R65" s="3"/>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3"/>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>385200</v>
+      </c>
+      <c r="E66" s="3">
         <v>952200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>598100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>710300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1184700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1284400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1258800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1154800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>264200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>18700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>10600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>6000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>800</v>
       </c>
-      <c r="P66" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R66" s="3"/>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3">
+        <v>0</v>
+      </c>
+      <c r="R66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S66" s="3"/>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3286,8 +3446,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3333,9 +3494,12 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-      <c r="R68" s="3"/>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3"/>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3381,9 +3545,12 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-      <c r="R69" s="3"/>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3"/>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3421,17 +3588,20 @@
         <v>0</v>
       </c>
       <c r="O70" s="3">
+        <v>0</v>
+      </c>
+      <c r="P70" s="3">
         <v>12200</v>
       </c>
-      <c r="P70" s="3">
+      <c r="Q70" s="3">
         <v>3900</v>
       </c>
-      <c r="Q70" s="3">
-        <v>0</v>
-      </c>
-      <c r="R70" s="3"/>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3"/>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3477,57 +3647,63 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-      <c r="R71" s="3"/>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3"/>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1015300</v>
+      </c>
+      <c r="E72" s="3">
         <v>910200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>891300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>771500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>736300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1293400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1072100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>779500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>391200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>7100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-13500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-17000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-3800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R72" s="3"/>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S72" s="3"/>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3573,9 +3749,12 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-      <c r="R73" s="3"/>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3"/>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3621,9 +3800,12 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-      <c r="R74" s="3"/>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3"/>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3669,57 +3851,63 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-      <c r="R75" s="3"/>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3"/>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1555300</v>
+      </c>
+      <c r="E76" s="3">
         <v>1540700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1664800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1562600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1644500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2242300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1943200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1589300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1034900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>87500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>67300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>69500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-3500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-900</v>
       </c>
-      <c r="Q76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R76" s="3"/>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S76" s="3"/>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3765,110 +3953,119 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-      <c r="R77" s="3"/>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3"/>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43100</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42735</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42369</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>42004</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41639</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41274</v>
       </c>
-      <c r="Q80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="R80" s="2"/>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="S80" s="2"/>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>115000</v>
+      </c>
+      <c r="E81" s="3">
         <v>142400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>276100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>215200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-458700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>322200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>426700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>409400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>330100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>19600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-13100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-2700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R81" s="3"/>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S81" s="3"/>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3887,56 +4084,60 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E83" s="3">
         <v>7200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>10500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>15500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>24500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>32000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>28500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>21600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>12100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>100</v>
       </c>
-      <c r="P83" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R83" s="3"/>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3">
+        <v>0</v>
+      </c>
+      <c r="R83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3982,9 +4183,12 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-      <c r="R84" s="3"/>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3"/>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4030,9 +4234,12 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-      <c r="R85" s="3"/>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3"/>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4078,9 +4285,12 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-      <c r="R86" s="3"/>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3"/>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4126,9 +4336,12 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-      <c r="R87" s="3"/>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3"/>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4174,57 +4387,63 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-      <c r="R88" s="3"/>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3"/>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>169200</v>
+      </c>
+      <c r="E89" s="3">
         <v>224700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>321100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>177900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>245400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>471900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>782600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>483800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>443600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>30100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>8200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-600</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R89" s="3"/>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S89" s="3"/>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4243,56 +4462,60 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-70400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-39100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-81300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-11700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-15000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-19000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-26800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-35300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-33600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-100</v>
       </c>
-      <c r="Q91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R91" s="3"/>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S91" s="3"/>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4338,9 +4561,12 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-      <c r="R92" s="3"/>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3"/>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4386,57 +4612,63 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-      <c r="R93" s="3"/>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3"/>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>23500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-76600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>340300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>248800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>401500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-114600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-578800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1458900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-28900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-16300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-47900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-300</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R94" s="3"/>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S94" s="3"/>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4455,32 +4687,33 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>49500</v>
+      </c>
+      <c r="E96" s="3">
         <v>98100</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>135100</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>121900</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>134200</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>172200</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>1400</v>
       </c>
-      <c r="J96" s="3">
-        <v>0</v>
-      </c>
       <c r="K96" s="3">
         <v>0</v>
       </c>
@@ -4502,9 +4735,12 @@
       <c r="Q96" s="3">
         <v>0</v>
       </c>
-      <c r="R96" s="3"/>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3"/>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4550,9 +4786,12 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-      <c r="R97" s="3"/>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3"/>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4598,9 +4837,12 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-      <c r="R98" s="3"/>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3"/>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4646,151 +4888,163 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-      <c r="R99" s="3"/>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3"/>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-777600</v>
+      </c>
+      <c r="E100" s="3">
         <v>32400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-239700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-497700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-281300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-229500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-182900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>681600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>400</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
       <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>-300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>65000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>6800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>3400</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R100" s="3"/>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S100" s="3"/>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-15800</v>
+      </c>
+      <c r="E101" s="3">
         <v>5800</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>13300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>6000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-6600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-12400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>3500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-4100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-1600</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-500</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-200</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
       <c r="P101" s="3">
         <v>0</v>
       </c>
-      <c r="Q101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R101" s="3"/>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S101" s="3"/>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-600700</v>
+      </c>
+      <c r="E102" s="3">
         <v>186300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>435000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-65000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>359100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>115400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>20800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-289900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>410900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>12200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-40400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>62400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>5600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>2500</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R102" s="3"/>
+      <c r="R102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
